--- a/artfynd/A 12489-2025 artfynd.xlsx
+++ b/artfynd/A 12489-2025 artfynd.xlsx
@@ -2083,10 +2083,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124458130</v>
+        <v>124462570</v>
       </c>
       <c r="B14" t="n">
-        <v>79892</v>
+        <v>79428</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460978</v>
+        <v>460850</v>
       </c>
       <c r="R14" t="n">
-        <v>7050963</v>
+        <v>7051224</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande sälg i gammal granskog på fuktig mark</t>
+          <t>På dimensionsavverkningsstubbe av tall i gammal gles barrblandskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2188,22 +2188,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124457982</v>
+        <v>124458130</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2216,46 +2216,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460959</v>
+        <v>460978</v>
       </c>
       <c r="R15" t="n">
-        <v>7050954</v>
+        <v>7050963</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2284,7 +2275,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2294,12 +2285,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På döda granar i gammal granskog på fuktig mark</t>
+          <t>På bark vid basen av gammal levande sälg i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2326,10 +2317,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124456762</v>
+        <v>124457982</v>
       </c>
       <c r="B16" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2342,34 +2333,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460943</v>
+        <v>460959</v>
       </c>
       <c r="R16" t="n">
-        <v>7050865</v>
+        <v>7050954</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På sälg ca 40 cm i diameter</t>
+          <t>På döda granar i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2431,22 +2431,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124462570</v>
+        <v>124456762</v>
       </c>
       <c r="B17" t="n">
-        <v>79428</v>
+        <v>79892</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2459,21 +2459,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2483,10 +2483,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460850</v>
+        <v>460943</v>
       </c>
       <c r="R17" t="n">
-        <v>7051224</v>
+        <v>7050865</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På dimensionsavverkningsstubbe av tall i gammal gles barrblandskog</t>
+          <t>På sälg ca 40 cm i diameter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2560,10 +2560,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124457172</v>
+        <v>124454537</v>
       </c>
       <c r="B18" t="n">
-        <v>100279</v>
+        <v>96985</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2576,34 +2576,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460933</v>
+        <v>460968</v>
       </c>
       <c r="R18" t="n">
-        <v>7050887</v>
+        <v>7050710</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2645,7 +2645,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2660,22 +2665,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124452541</v>
+        <v>124457172</v>
       </c>
       <c r="B19" t="n">
-        <v>77743</v>
+        <v>100279</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2684,25 +2689,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228579</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2712,10 +2717,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461068</v>
+        <v>460933</v>
       </c>
       <c r="R19" t="n">
-        <v>7050690</v>
+        <v>7050887</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2747,7 +2752,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2757,12 +2762,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På gran ca 45 cm i diameter i äldre granskog</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2789,7 +2789,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124457471</v>
+        <v>124452541</v>
       </c>
       <c r="B20" t="n">
         <v>77743</v>
@@ -2829,10 +2829,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460904</v>
+        <v>461068</v>
       </c>
       <c r="R20" t="n">
-        <v>7050918</v>
+        <v>7050690</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre granskog</t>
+          <t>På gran ca 45 cm i diameter i äldre granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2906,7 +2906,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124460183</v>
+        <v>124457471</v>
       </c>
       <c r="B21" t="n">
         <v>77743</v>
@@ -2942,14 +2942,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460867</v>
+        <v>460904</v>
       </c>
       <c r="R21" t="n">
-        <v>7051147</v>
+        <v>7050918</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (ca 180 år gammal) i gammal granskog i fuktig sänka</t>
+          <t>På gran ca 35 cm i diameter i äldre granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3011,22 +3011,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124454537</v>
+        <v>124460183</v>
       </c>
       <c r="B22" t="n">
-        <v>96985</v>
+        <v>77743</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3035,38 +3035,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221941</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460968</v>
+        <v>460867</v>
       </c>
       <c r="R22" t="n">
-        <v>7050710</v>
+        <v>7051147</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (ca 180 år gammal) i gammal granskog i fuktig sänka</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -7136,10 +7136,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124450168</v>
+        <v>124459186</v>
       </c>
       <c r="B57" t="n">
-        <v>57666</v>
+        <v>74901</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7152,51 +7152,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461133</v>
+        <v>460885</v>
       </c>
       <c r="R57" t="n">
-        <v>7050555</v>
+        <v>7051041</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7225,7 +7211,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7235,12 +7221,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>I gammal granskog omgiven av sumpskog och myr</t>
+          <t>På gran ca 50 cm i diameter</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7255,12 +7241,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7384,10 +7370,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124459560</v>
+        <v>124450168</v>
       </c>
       <c r="B59" t="n">
-        <v>91012</v>
+        <v>57666</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7400,37 +7386,51 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>460899</v>
+        <v>461133</v>
       </c>
       <c r="R59" t="n">
-        <v>7051069</v>
+        <v>7050555</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På granlåga ca 35 cm i diameter, ligger över en bäck i en liten svacka/ravin</t>
+          <t>I gammal granskog omgiven av sumpskog och myr</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7489,12 +7489,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7618,10 +7618,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124459186</v>
+        <v>124459560</v>
       </c>
       <c r="B61" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7634,21 +7634,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7658,10 +7658,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>460885</v>
+        <v>460899</v>
       </c>
       <c r="R61" t="n">
-        <v>7051041</v>
+        <v>7051069</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På gran ca 50 cm i diameter</t>
+          <t>På granlåga ca 35 cm i diameter, ligger över en bäck i en liten svacka/ravin</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -11362,10 +11362,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124452642</v>
+        <v>124457081</v>
       </c>
       <c r="B93" t="n">
-        <v>100279</v>
+        <v>77743</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11374,25 +11374,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222498</v>
+        <v>228579</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11402,10 +11402,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461064</v>
+        <v>460936</v>
       </c>
       <c r="R93" t="n">
-        <v>7050693</v>
+        <v>7050880</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11437,7 +11437,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11447,7 +11447,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>På gran ca 35 cm i diameter</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11474,10 +11479,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124457081</v>
+        <v>124452642</v>
       </c>
       <c r="B94" t="n">
-        <v>77743</v>
+        <v>100279</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11486,25 +11491,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228579</v>
+        <v>222498</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11514,10 +11519,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>460936</v>
+        <v>461064</v>
       </c>
       <c r="R94" t="n">
-        <v>7050880</v>
+        <v>7050693</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11549,7 +11554,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11559,12 +11564,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>På gran ca 35 cm i diameter</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11591,10 +11591,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124447967</v>
+        <v>124454602</v>
       </c>
       <c r="B95" t="n">
-        <v>77743</v>
+        <v>78891</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11607,34 +11607,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228579</v>
+        <v>283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461232</v>
+        <v>460996</v>
       </c>
       <c r="R95" t="n">
-        <v>7050456</v>
+        <v>7050828</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11666,7 +11666,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11676,12 +11676,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På gran ca 22 cm i diameter  i äldre med tallinslag</t>
+          <t>På gran med avbruten topp ca 6 cm i diameter i äldre granskog på frisk-fuktig mark</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11708,10 +11708,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124454602</v>
+        <v>124467315</v>
       </c>
       <c r="B96" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11724,34 +11724,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>460996</v>
+        <v>461165</v>
       </c>
       <c r="R96" t="n">
-        <v>7050828</v>
+        <v>7050419</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11783,7 +11783,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11793,12 +11793,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På gran med avbruten topp ca 6 cm i diameter i äldre granskog på frisk-fuktig mark</t>
+          <t>På gammal gran (ca 170 år) i gammal granskog vid sumpmyr</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11813,22 +11813,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124450863</v>
+        <v>124456509</v>
       </c>
       <c r="B97" t="n">
-        <v>56714</v>
+        <v>57883</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11837,20 +11837,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>102612</v>
+        <v>103015</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -11874,10 +11874,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>461150</v>
+        <v>460910</v>
       </c>
       <c r="R97" t="n">
-        <v>7050646</v>
+        <v>7050839</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11909,7 +11909,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11919,12 +11919,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>I gammal granskog vid källflöde</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11951,10 +11951,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124467315</v>
+        <v>124450863</v>
       </c>
       <c r="B98" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11967,34 +11967,43 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>461165</v>
+        <v>461150</v>
       </c>
       <c r="R98" t="n">
-        <v>7050419</v>
+        <v>7050646</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12026,7 +12035,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12036,12 +12045,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 170 år) i gammal granskog vid sumpmyr</t>
+          <t>I gammal granskog vid källflöde</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12068,10 +12077,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124456509</v>
+        <v>124447967</v>
       </c>
       <c r="B99" t="n">
-        <v>57883</v>
+        <v>77743</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12080,47 +12089,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>103015</v>
+        <v>228579</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>460910</v>
+        <v>461232</v>
       </c>
       <c r="R99" t="n">
-        <v>7050839</v>
+        <v>7050456</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12152,7 +12152,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På gran ca 22 cm i diameter  i äldre med tallinslag</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12182,12 +12182,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -12428,10 +12428,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124455015</v>
+        <v>124451344</v>
       </c>
       <c r="B102" t="n">
-        <v>57454</v>
+        <v>77753</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12440,50 +12440,41 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>102622</v>
+        <v>314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>460885</v>
+        <v>461120</v>
       </c>
       <c r="R102" t="n">
-        <v>7050930</v>
+        <v>7050636</v>
       </c>
       <c r="S102" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12512,7 +12503,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12522,7 +12513,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>På undersidan av gren på senvuxen gran ca 16 cm i diameter, intill bäck</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12537,22 +12533,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124459858</v>
+        <v>124466220</v>
       </c>
       <c r="B103" t="n">
-        <v>77743</v>
+        <v>91030</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12565,21 +12561,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12589,10 +12585,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>460871</v>
+        <v>460940</v>
       </c>
       <c r="R103" t="n">
-        <v>7051122</v>
+        <v>7050559</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12624,7 +12620,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12634,12 +12630,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter</t>
+          <t>På levande gran I äldre granskog</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13017,10 +13013,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124451344</v>
+        <v>124455015</v>
       </c>
       <c r="B107" t="n">
-        <v>77753</v>
+        <v>57454</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13029,41 +13025,50 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>314</v>
+        <v>102622</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>461120</v>
+        <v>460885</v>
       </c>
       <c r="R107" t="n">
-        <v>7050636</v>
+        <v>7050930</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13092,7 +13097,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13102,12 +13107,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>På undersidan av gren på senvuxen gran ca 16 cm i diameter, intill bäck</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13122,22 +13122,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124466220</v>
+        <v>124459858</v>
       </c>
       <c r="B108" t="n">
-        <v>91030</v>
+        <v>77743</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13150,21 +13150,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -13174,10 +13174,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>460940</v>
+        <v>460871</v>
       </c>
       <c r="R108" t="n">
-        <v>7050559</v>
+        <v>7051122</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13219,12 +13219,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>På levande gran I äldre granskog</t>
+          <t>På gran ca 35 cm i diameter</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -16448,10 +16448,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>124463372</v>
+        <v>124458517</v>
       </c>
       <c r="B136" t="n">
-        <v>79851</v>
+        <v>79892</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16460,25 +16460,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -16488,10 +16488,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>460809</v>
+        <v>460887</v>
       </c>
       <c r="R136" t="n">
-        <v>7051220</v>
+        <v>7051004</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16523,7 +16523,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16533,12 +16533,12 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>På döende sälg ca 45 cm i diameter I gammal barrblandskog</t>
+          <t>På sälg ca 45 cm i diameter</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16565,10 +16565,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>124447135</v>
+        <v>124452019</v>
       </c>
       <c r="B137" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16577,25 +16577,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -16605,10 +16605,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>461248</v>
+        <v>461089</v>
       </c>
       <c r="R137" t="n">
-        <v>7050401</v>
+        <v>7050682</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16640,7 +16640,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16650,12 +16650,12 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16675,17 +16675,17 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>124448067</v>
+        <v>124467045</v>
       </c>
       <c r="B138" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16694,38 +16694,38 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>461238</v>
+        <v>461086</v>
       </c>
       <c r="R138" t="n">
-        <v>7050458</v>
+        <v>7050465</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16757,7 +16757,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16767,12 +16767,12 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>På gran ca 45 cm i diameter i äldre granskog med inslag av tall</t>
+          <t>På rönn I äldre granskog</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16799,10 +16799,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>124449598</v>
+        <v>124457780</v>
       </c>
       <c r="B139" t="n">
-        <v>91030</v>
+        <v>74885</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16811,25 +16811,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -16839,10 +16839,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>461116</v>
+        <v>460884</v>
       </c>
       <c r="R139" t="n">
-        <v>7050579</v>
+        <v>7050944</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16874,7 +16874,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>På död del av levande gran ca 5 m från en bäck i äldre granskog</t>
+          <t>På ved på gråalshögstubbe i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16904,22 +16904,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>124458517</v>
+        <v>124465980</v>
       </c>
       <c r="B140" t="n">
-        <v>79892</v>
+        <v>74901</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16932,21 +16932,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -16956,10 +16956,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>460887</v>
+        <v>460929</v>
       </c>
       <c r="R140" t="n">
-        <v>7051004</v>
+        <v>7050642</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16991,7 +16991,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -17001,12 +17001,12 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>På sälg ca 45 cm i diameter</t>
+          <t>På gran 20 cm i diameter I äldre granskog</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -17033,10 +17033,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>124452019</v>
+        <v>124466463</v>
       </c>
       <c r="B141" t="n">
-        <v>79927</v>
+        <v>74901</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -17045,38 +17045,38 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>461089</v>
+        <v>460999</v>
       </c>
       <c r="R141" t="n">
-        <v>7050682</v>
+        <v>7050500</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17108,7 +17108,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -17118,12 +17118,12 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På gran ca 30 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17138,22 +17138,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>124467045</v>
+        <v>124463372</v>
       </c>
       <c r="B142" t="n">
-        <v>79920</v>
+        <v>79851</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -17166,21 +17166,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -17190,10 +17190,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>461086</v>
+        <v>460809</v>
       </c>
       <c r="R142" t="n">
-        <v>7050465</v>
+        <v>7051220</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17225,7 +17225,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -17235,12 +17235,12 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>På rönn I äldre granskog</t>
+          <t>På döende sälg ca 45 cm i diameter I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17267,10 +17267,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>124457780</v>
+        <v>124447135</v>
       </c>
       <c r="B143" t="n">
-        <v>74885</v>
+        <v>78810</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -17279,25 +17279,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -17307,10 +17307,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>460884</v>
+        <v>461248</v>
       </c>
       <c r="R143" t="n">
-        <v>7050944</v>
+        <v>7050401</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17342,7 +17342,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -17352,12 +17352,12 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>På ved på gråalshögstubbe i gammal granskog på fuktig mark</t>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17377,14 +17377,14 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>124465980</v>
+        <v>124448067</v>
       </c>
       <c r="B144" t="n">
         <v>74901</v>
@@ -17420,14 +17420,14 @@
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>460929</v>
+        <v>461238</v>
       </c>
       <c r="R144" t="n">
-        <v>7050642</v>
+        <v>7050458</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17459,7 +17459,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -17469,12 +17469,12 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>På gran 20 cm i diameter I äldre granskog</t>
+          <t>På gran ca 45 cm i diameter i äldre granskog med inslag av tall</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17501,10 +17501,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>124466463</v>
+        <v>124449598</v>
       </c>
       <c r="B145" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -17517,34 +17517,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>460999</v>
+        <v>461116</v>
       </c>
       <c r="R145" t="n">
-        <v>7050500</v>
+        <v>7050579</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -17586,12 +17586,12 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>På gran ca 30 cm i diameter i äldre barrblandskog</t>
+          <t>På död del av levande gran ca 5 m från en bäck i äldre granskog</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17618,10 +17618,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>124452305</v>
+        <v>124455697</v>
       </c>
       <c r="B146" t="n">
-        <v>79926</v>
+        <v>57513</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -17630,41 +17630,46 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>461106</v>
+        <v>460906</v>
       </c>
       <c r="R146" t="n">
-        <v>7050697</v>
+        <v>7050839</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -17693,7 +17698,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17703,12 +17708,12 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal grov sälg i gammal granskog</t>
+          <t>Lite äldre ringhack på gammal gran i gammal granskog på ås</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17728,17 +17733,17 @@
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>124455107</v>
+        <v>124451835</v>
       </c>
       <c r="B147" t="n">
-        <v>79920</v>
+        <v>90977</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -17751,34 +17756,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>460938</v>
+        <v>461102</v>
       </c>
       <c r="R147" t="n">
-        <v>7050831</v>
+        <v>7050652</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17810,7 +17815,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17820,12 +17825,12 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>På död rönn ca 18 cm i diameter</t>
+          <t>På granlåga i gammal granskog vid källflöde</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17840,22 +17845,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>124459044</v>
+        <v>124458954</v>
       </c>
       <c r="B148" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17868,21 +17873,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17892,10 +17897,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>460900</v>
+        <v>460891</v>
       </c>
       <c r="R148" t="n">
-        <v>7051032</v>
+        <v>7051023</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17927,7 +17932,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17937,12 +17942,12 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter</t>
+          <t>Ett 30-tal bålar på 3 granar</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17969,10 +17974,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>124452111</v>
+        <v>124452305</v>
       </c>
       <c r="B149" t="n">
-        <v>79826</v>
+        <v>79926</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17985,21 +17990,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6457</v>
+        <v>6463</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -18009,10 +18014,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>461089</v>
+        <v>461106</v>
       </c>
       <c r="R149" t="n">
-        <v>7050682</v>
+        <v>7050697</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -18044,7 +18049,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -18054,12 +18059,12 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På bark på stam av levande gammal grov sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18086,10 +18091,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>124455697</v>
+        <v>124455107</v>
       </c>
       <c r="B150" t="n">
-        <v>57513</v>
+        <v>79920</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -18098,46 +18103,41 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>460906</v>
+        <v>460938</v>
       </c>
       <c r="R150" t="n">
-        <v>7050839</v>
+        <v>7050831</v>
       </c>
       <c r="S150" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -18176,12 +18176,12 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Lite äldre ringhack på gammal gran i gammal granskog på ås</t>
+          <t>På död rönn ca 18 cm i diameter</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18196,22 +18196,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>124451835</v>
+        <v>124459044</v>
       </c>
       <c r="B151" t="n">
-        <v>90977</v>
+        <v>74901</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -18220,38 +18220,38 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>461102</v>
+        <v>460900</v>
       </c>
       <c r="R151" t="n">
-        <v>7050652</v>
+        <v>7051032</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -18283,7 +18283,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -18293,12 +18293,12 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog vid källflöde</t>
+          <t>På gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18313,22 +18313,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124458954</v>
+        <v>124452111</v>
       </c>
       <c r="B152" t="n">
-        <v>78810</v>
+        <v>79826</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -18337,38 +18337,38 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>460891</v>
+        <v>461089</v>
       </c>
       <c r="R152" t="n">
-        <v>7051023</v>
+        <v>7050682</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18400,7 +18400,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -18410,12 +18410,12 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Ett 30-tal bålar på 3 granar</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18430,22 +18430,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124465641</v>
+        <v>124459297</v>
       </c>
       <c r="B153" t="n">
-        <v>97185</v>
+        <v>105102</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -18458,37 +18458,37 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220686</v>
+        <v>221725</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>460931</v>
+        <v>460876</v>
       </c>
       <c r="R153" t="n">
-        <v>7050680</v>
+        <v>7051057</v>
       </c>
       <c r="S153" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -18517,7 +18517,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -18527,7 +18527,12 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>På marken vid bäck i gammal granskog</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18542,22 +18547,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124459297</v>
+        <v>124465641</v>
       </c>
       <c r="B154" t="n">
-        <v>105102</v>
+        <v>97185</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -18570,37 +18575,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>221725</v>
+        <v>220686</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>460876</v>
+        <v>460931</v>
       </c>
       <c r="R154" t="n">
-        <v>7051057</v>
+        <v>7050680</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -18629,7 +18634,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -18639,12 +18644,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>På marken vid bäck i gammal granskog</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18659,22 +18659,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124452003</v>
+        <v>124453554</v>
       </c>
       <c r="B155" t="n">
-        <v>79851</v>
+        <v>91012</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18683,25 +18683,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -18711,10 +18711,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>461089</v>
+        <v>461012</v>
       </c>
       <c r="R155" t="n">
-        <v>7050682</v>
+        <v>7050679</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18746,7 +18746,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18756,12 +18756,12 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På granlåga i fuktigt läge vid bäckdråg, i gammal granskog</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18781,17 +18781,17 @@
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124452969</v>
+        <v>124459298</v>
       </c>
       <c r="B156" t="n">
-        <v>77743</v>
+        <v>79927</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18800,25 +18800,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -18828,10 +18828,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>461058</v>
+        <v>460882</v>
       </c>
       <c r="R156" t="n">
-        <v>7050696</v>
+        <v>7051046</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18863,7 +18863,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18873,12 +18873,12 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>På gammal gran ca 30 cm I diameter</t>
+          <t>På sälg ca 40 cm i diameter</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18905,10 +18905,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>124464548</v>
+        <v>124455549</v>
       </c>
       <c r="B157" t="n">
-        <v>77743</v>
+        <v>79920</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18917,25 +18917,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -18945,10 +18945,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>460857</v>
+        <v>460935</v>
       </c>
       <c r="R157" t="n">
-        <v>7051101</v>
+        <v>7050779</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18980,7 +18980,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18990,12 +18990,12 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>På senvuxen gran ca 15 cm i diameter I gammal barrblandskog</t>
+          <t>På sälg ca 45 cm i diameter</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -19022,10 +19022,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>124447866</v>
+        <v>124456983</v>
       </c>
       <c r="B158" t="n">
-        <v>79857</v>
+        <v>100279</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -19038,21 +19038,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>229748</v>
+        <v>222498</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -19062,10 +19062,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>461220</v>
+        <v>460930</v>
       </c>
       <c r="R158" t="n">
-        <v>7050419</v>
+        <v>7050862</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -19097,7 +19097,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -19107,12 +19107,12 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>På död jolster vid bäck i fuktig gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -19132,17 +19132,17 @@
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>124453554</v>
+        <v>124452003</v>
       </c>
       <c r="B159" t="n">
-        <v>91012</v>
+        <v>79851</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -19151,25 +19151,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -19179,10 +19179,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>461012</v>
+        <v>461089</v>
       </c>
       <c r="R159" t="n">
-        <v>7050679</v>
+        <v>7050682</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19224,12 +19224,12 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>På granlåga i fuktigt läge vid bäckdråg, i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19249,17 +19249,17 @@
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>124459298</v>
+        <v>124452969</v>
       </c>
       <c r="B160" t="n">
-        <v>79927</v>
+        <v>77743</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -19268,25 +19268,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6464</v>
+        <v>228579</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -19296,10 +19296,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>460882</v>
+        <v>461058</v>
       </c>
       <c r="R160" t="n">
-        <v>7051046</v>
+        <v>7050696</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19331,7 +19331,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19341,12 +19341,12 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>På sälg ca 40 cm i diameter</t>
+          <t>På gammal gran ca 30 cm I diameter</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19373,10 +19373,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>124455549</v>
+        <v>124464548</v>
       </c>
       <c r="B161" t="n">
-        <v>79920</v>
+        <v>77743</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -19385,25 +19385,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6462</v>
+        <v>228579</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -19413,10 +19413,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>460935</v>
+        <v>460857</v>
       </c>
       <c r="R161" t="n">
-        <v>7050779</v>
+        <v>7051101</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19448,7 +19448,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>På sälg ca 45 cm i diameter</t>
+          <t>På senvuxen gran ca 15 cm i diameter I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19490,10 +19490,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>124456983</v>
+        <v>124447866</v>
       </c>
       <c r="B162" t="n">
-        <v>100279</v>
+        <v>79857</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -19506,21 +19506,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>222498</v>
+        <v>229748</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -19530,10 +19530,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>460930</v>
+        <v>461220</v>
       </c>
       <c r="R162" t="n">
-        <v>7050862</v>
+        <v>7050419</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19565,7 +19565,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -19575,12 +19575,12 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På död jolster vid bäck i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19600,7 +19600,7 @@
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>

--- a/artfynd/A 12489-2025 artfynd.xlsx
+++ b/artfynd/A 12489-2025 artfynd.xlsx
@@ -3257,10 +3257,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124464583</v>
+        <v>124463955</v>
       </c>
       <c r="B24" t="n">
-        <v>57529</v>
+        <v>78547</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3273,39 +3273,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460856</v>
+        <v>460891</v>
       </c>
       <c r="R24" t="n">
-        <v>7051060</v>
+        <v>7051196</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3337,7 +3332,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3347,12 +3342,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Födosökshack efter hästmyror på gammal levande gran i gammal granskog</t>
+          <t>På kolad ved på gammal tallhögstubbe i gammal barrblandskog på blockig mark i sydsluttning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3379,10 +3374,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124453757</v>
+        <v>124463287</v>
       </c>
       <c r="B25" t="n">
-        <v>77743</v>
+        <v>78547</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3395,21 +3390,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228579</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3419,10 +3414,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460989</v>
+        <v>460818</v>
       </c>
       <c r="R25" t="n">
-        <v>7050753</v>
+        <v>7051226</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3454,7 +3449,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3464,12 +3459,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gran ca 45 cm i diameter</t>
+          <t>På bränd högstubbe av tall ca 20 cm i diameter och 4 meter hög i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3496,10 +3491,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124451578</v>
+        <v>124455021</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3512,37 +3507,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461108</v>
+        <v>460949</v>
       </c>
       <c r="R26" t="n">
-        <v>7050663</v>
+        <v>7050826</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3571,7 +3566,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3581,12 +3576,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog vid källflöde</t>
+          <t>På gran ca 40 cm i diameter i äldre granskog på frisk-fuktig mark</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3601,22 +3596,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124464945</v>
+        <v>124459961</v>
       </c>
       <c r="B27" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3625,25 +3620,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3653,10 +3648,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460854</v>
+        <v>460864</v>
       </c>
       <c r="R27" t="n">
-        <v>7050992</v>
+        <v>7051145</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3688,7 +3683,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3698,12 +3693,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter ca 7 m från bäck i gammal granskog</t>
+          <t>På sälg ca 18 cm i diameter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3730,10 +3725,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124449149</v>
+        <v>124463409</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3746,46 +3741,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461138</v>
+        <v>460811</v>
       </c>
       <c r="R28" t="n">
-        <v>7050552</v>
+        <v>7051224</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3814,7 +3800,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3824,12 +3810,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På högstubbe av gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3844,22 +3830,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124463955</v>
+        <v>124459298</v>
       </c>
       <c r="B29" t="n">
-        <v>78547</v>
+        <v>79927</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3868,38 +3854,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460891</v>
+        <v>460882</v>
       </c>
       <c r="R29" t="n">
-        <v>7051196</v>
+        <v>7051046</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3931,7 +3917,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3941,12 +3927,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallhögstubbe i gammal barrblandskog på blockig mark i sydsluttning</t>
+          <t>På sälg ca 40 cm i diameter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3961,22 +3947,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124463287</v>
+        <v>124457291</v>
       </c>
       <c r="B30" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3989,21 +3975,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4013,10 +3999,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460818</v>
+        <v>460917</v>
       </c>
       <c r="R30" t="n">
-        <v>7051226</v>
+        <v>7050904</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4048,7 +4034,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4058,12 +4044,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På bränd högstubbe av tall ca 20 cm i diameter och 4 meter hög i gammal barrblandskog</t>
+          <t>Ett tiotal bålar på en gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4090,10 +4076,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124455021</v>
+        <v>124463334</v>
       </c>
       <c r="B31" t="n">
-        <v>74901</v>
+        <v>78546</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4106,21 +4092,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4130,10 +4116,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460949</v>
+        <v>460817</v>
       </c>
       <c r="R31" t="n">
-        <v>7050826</v>
+        <v>7051224</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4165,7 +4151,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4175,12 +4161,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran ca 40 cm i diameter i äldre granskog på frisk-fuktig mark</t>
+          <t>På bränd högstubbe av tall I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4207,10 +4193,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124459961</v>
+        <v>124464044</v>
       </c>
       <c r="B32" t="n">
-        <v>79920</v>
+        <v>78455</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4219,38 +4205,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460864</v>
+        <v>460886</v>
       </c>
       <c r="R32" t="n">
-        <v>7051145</v>
+        <v>7051158</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4282,7 +4268,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4292,12 +4278,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På sälg ca 18 cm i diameter</t>
+          <t>På ved på gammal tallrot på tallåga i gammal barrblandskog i sydsluttning</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4312,22 +4298,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124463409</v>
+        <v>124464945</v>
       </c>
       <c r="B33" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4340,21 +4326,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4364,10 +4350,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460811</v>
+        <v>460854</v>
       </c>
       <c r="R33" t="n">
-        <v>7051224</v>
+        <v>7050992</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4399,7 +4385,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4409,12 +4395,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På högstubbe av gran</t>
+          <t>På gran ca 35 cm i diameter ca 7 m från bäck i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4441,10 +4427,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124459298</v>
+        <v>124464583</v>
       </c>
       <c r="B34" t="n">
-        <v>79927</v>
+        <v>57529</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4453,38 +4439,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460882</v>
+        <v>460856</v>
       </c>
       <c r="R34" t="n">
-        <v>7051046</v>
+        <v>7051060</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4516,7 +4507,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4526,12 +4517,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På sälg ca 40 cm i diameter</t>
+          <t>Födosökshack efter hästmyror på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4546,22 +4537,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124457291</v>
+        <v>124453757</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4574,21 +4565,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4598,10 +4589,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>460917</v>
+        <v>460989</v>
       </c>
       <c r="R35" t="n">
-        <v>7050904</v>
+        <v>7050753</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4633,7 +4624,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4643,12 +4634,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ett tiotal bålar på en gran</t>
+          <t>På gran ca 45 cm i diameter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4675,10 +4666,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124463334</v>
+        <v>124451578</v>
       </c>
       <c r="B36" t="n">
-        <v>78546</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4691,37 +4682,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>460817</v>
+        <v>461108</v>
       </c>
       <c r="R36" t="n">
-        <v>7051224</v>
+        <v>7050663</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4750,7 +4741,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4760,12 +4751,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På bränd högstubbe av tall I gammal barrblandskog</t>
+          <t>På granlåga i gammal granskog vid källflöde</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4780,22 +4771,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124464044</v>
+        <v>124449149</v>
       </c>
       <c r="B37" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4808,37 +4799,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460886</v>
+        <v>461138</v>
       </c>
       <c r="R37" t="n">
-        <v>7051158</v>
+        <v>7050552</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På ved på gammal tallrot på tallåga i gammal barrblandskog i sydsluttning</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5962,10 +5962,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124447566</v>
+        <v>124451835</v>
       </c>
       <c r="B47" t="n">
-        <v>74901</v>
+        <v>90977</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5974,25 +5974,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6002,10 +6002,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461239</v>
+        <v>461102</v>
       </c>
       <c r="R47" t="n">
-        <v>7050406</v>
+        <v>7050652</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6037,7 +6037,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gran ca 30 cm i diameter i äldre granskog på fuktig mark</t>
+          <t>På granlåga i gammal granskog vid källflöde</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6067,22 +6067,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124467045</v>
+        <v>124447566</v>
       </c>
       <c r="B48" t="n">
-        <v>79920</v>
+        <v>74901</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6091,38 +6091,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461086</v>
+        <v>461239</v>
       </c>
       <c r="R48" t="n">
-        <v>7050465</v>
+        <v>7050406</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På rönn I äldre granskog</t>
+          <t>På gran ca 30 cm i diameter i äldre granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6196,10 +6196,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124459186</v>
+        <v>124467045</v>
       </c>
       <c r="B49" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6208,25 +6208,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6236,10 +6236,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>460885</v>
+        <v>461086</v>
       </c>
       <c r="R49" t="n">
-        <v>7051041</v>
+        <v>7050465</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gran ca 50 cm i diameter</t>
+          <t>På rönn I äldre granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6313,10 +6313,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124458497</v>
+        <v>124454121</v>
       </c>
       <c r="B50" t="n">
-        <v>91012</v>
+        <v>91950</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6325,25 +6325,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6353,10 +6353,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>460925</v>
+        <v>461008</v>
       </c>
       <c r="R50" t="n">
-        <v>7051037</v>
+        <v>7050615</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gammal granlåga i kanten av gammal granskog</t>
+          <t>På marken i bäckdråg  med gammal granskog med rikligt med död ved</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6430,10 +6430,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124454121</v>
+        <v>124459186</v>
       </c>
       <c r="B51" t="n">
-        <v>91950</v>
+        <v>74901</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6442,38 +6442,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4769</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461008</v>
+        <v>460885</v>
       </c>
       <c r="R51" t="n">
-        <v>7050615</v>
+        <v>7051041</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6505,7 +6505,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6515,12 +6515,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På marken i bäckdråg  med gammal granskog med rikligt med död ved</t>
+          <t>På gran ca 50 cm i diameter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6535,22 +6535,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124451835</v>
+        <v>124458497</v>
       </c>
       <c r="B52" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6559,25 +6559,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461102</v>
+        <v>460925</v>
       </c>
       <c r="R52" t="n">
-        <v>7050652</v>
+        <v>7051037</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6632,12 +6632,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog vid källflöde</t>
+          <t>På gammal granlåga i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7375,10 +7375,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124457780</v>
+        <v>124458121</v>
       </c>
       <c r="B59" t="n">
-        <v>74885</v>
+        <v>78810</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7387,38 +7387,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>460884</v>
+        <v>460890</v>
       </c>
       <c r="R59" t="n">
-        <v>7050944</v>
+        <v>7050973</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På ved på gråalshögstubbe i gammal granskog på fuktig mark</t>
+          <t>Ett 30-tal bålar på en gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7480,19 +7480,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124458121</v>
+        <v>124448916</v>
       </c>
       <c r="B60" t="n">
         <v>78810</v>
@@ -7528,14 +7528,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>460890</v>
+        <v>461180</v>
       </c>
       <c r="R60" t="n">
-        <v>7050973</v>
+        <v>7050497</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ett 30-tal bålar på en gran</t>
+          <t>På gamla granar i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7597,22 +7597,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124448916</v>
+        <v>124448067</v>
       </c>
       <c r="B61" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7625,21 +7625,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7649,10 +7649,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461180</v>
+        <v>461238</v>
       </c>
       <c r="R61" t="n">
-        <v>7050497</v>
+        <v>7050458</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal fuktig granskog</t>
+          <t>På gran ca 45 cm i diameter i äldre granskog med inslag av tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7714,12 +7714,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7838,10 +7838,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124450918</v>
+        <v>124465552</v>
       </c>
       <c r="B63" t="n">
-        <v>79927</v>
+        <v>79892</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7850,38 +7850,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461131</v>
+        <v>460923</v>
       </c>
       <c r="R63" t="n">
-        <v>7050604</v>
+        <v>7050686</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7913,7 +7913,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På högstubbe av gråal ca 1 m från en bäck</t>
+          <t>På bark på stam av levande sälg i äldre granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7943,22 +7943,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124462929</v>
+        <v>124450918</v>
       </c>
       <c r="B64" t="n">
-        <v>79428</v>
+        <v>79927</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7967,41 +7967,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>460814</v>
+        <v>461131</v>
       </c>
       <c r="R64" t="n">
-        <v>7051237</v>
+        <v>7050604</v>
       </c>
       <c r="S64" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På bränd högstubbe av tall i gammal barrblandskog</t>
+          <t>På högstubbe av gråal ca 1 m från en bäck</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8072,10 +8072,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124457471</v>
+        <v>124462929</v>
       </c>
       <c r="B65" t="n">
-        <v>77743</v>
+        <v>79428</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8088,21 +8088,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228579</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8112,13 +8112,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>460904</v>
+        <v>460814</v>
       </c>
       <c r="R65" t="n">
-        <v>7050918</v>
+        <v>7051237</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8157,12 +8157,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre granskog</t>
+          <t>På bränd högstubbe av tall i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8189,10 +8189,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124448067</v>
+        <v>124457471</v>
       </c>
       <c r="B66" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8205,34 +8205,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461238</v>
+        <v>460904</v>
       </c>
       <c r="R66" t="n">
-        <v>7050458</v>
+        <v>7050918</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8264,7 +8264,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På gran ca 45 cm i diameter i äldre granskog med inslag av tall</t>
+          <t>På gran ca 35 cm i diameter i äldre granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8306,10 +8306,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124465552</v>
+        <v>124457780</v>
       </c>
       <c r="B67" t="n">
-        <v>79892</v>
+        <v>74885</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8318,38 +8318,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>460923</v>
+        <v>460884</v>
       </c>
       <c r="R67" t="n">
-        <v>7050686</v>
+        <v>7050944</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8381,7 +8381,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg i äldre granskog</t>
+          <t>På ved på gråalshögstubbe i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -11006,10 +11006,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124464212</v>
+        <v>124452019</v>
       </c>
       <c r="B90" t="n">
-        <v>78547</v>
+        <v>79927</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11018,41 +11018,41 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>6464</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>460841</v>
+        <v>461089</v>
       </c>
       <c r="R90" t="n">
-        <v>7051180</v>
+        <v>7050682</v>
       </c>
       <c r="S90" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallhögstubbe i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11123,10 +11123,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124459079</v>
+        <v>124464212</v>
       </c>
       <c r="B91" t="n">
-        <v>91012</v>
+        <v>78547</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11139,21 +11139,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11163,13 +11163,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>460903</v>
+        <v>460841</v>
       </c>
       <c r="R91" t="n">
-        <v>7051049</v>
+        <v>7051180</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På kolad ved på gammal tallhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11240,10 +11240,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124458734</v>
+        <v>124459079</v>
       </c>
       <c r="B92" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11256,37 +11256,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>460884</v>
+        <v>460903</v>
       </c>
       <c r="R92" t="n">
-        <v>7050999</v>
+        <v>7051049</v>
       </c>
       <c r="S92" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>1 spelande</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11345,22 +11345,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124457379</v>
+        <v>124458734</v>
       </c>
       <c r="B93" t="n">
-        <v>91950</v>
+        <v>56714</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11369,41 +11369,41 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4769</v>
+        <v>102612</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>460878</v>
+        <v>460884</v>
       </c>
       <c r="R93" t="n">
-        <v>7050927</v>
+        <v>7050999</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11442,12 +11442,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På marken i gammal fuktig granskog</t>
+          <t>1 spelande</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11462,22 +11462,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124452019</v>
+        <v>124457379</v>
       </c>
       <c r="B94" t="n">
-        <v>79927</v>
+        <v>91950</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11490,21 +11490,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6464</v>
+        <v>4769</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11514,10 +11514,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461089</v>
+        <v>460878</v>
       </c>
       <c r="R94" t="n">
-        <v>7050682</v>
+        <v>7050927</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11559,12 +11559,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På marken i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -16293,10 +16293,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124459477</v>
+        <v>124447855</v>
       </c>
       <c r="B135" t="n">
-        <v>57529</v>
+        <v>79920</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16305,46 +16305,41 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>460890</v>
+        <v>461216</v>
       </c>
       <c r="R135" t="n">
-        <v>7051075</v>
+        <v>7050415</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16373,7 +16368,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -16383,12 +16378,12 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Födosökspår efter hästmyror</t>
+          <t>På bark på död stam av jolster i fuktig gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16408,7 +16403,7 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -16649,10 +16644,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>124454161</v>
+        <v>124462439</v>
       </c>
       <c r="B138" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16665,21 +16660,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -16689,10 +16684,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>461010</v>
+        <v>460848</v>
       </c>
       <c r="R138" t="n">
-        <v>7050791</v>
+        <v>7051206</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16724,7 +16719,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16734,12 +16729,12 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>Ett tiotal bålar på en gran</t>
+          <t>På dimensionsavverkningsstubbe av tall i gammal gles barrblandskog</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16766,10 +16761,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>124462439</v>
+        <v>124459477</v>
       </c>
       <c r="B139" t="n">
-        <v>79428</v>
+        <v>57529</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16782,34 +16777,39 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>460848</v>
+        <v>460890</v>
       </c>
       <c r="R139" t="n">
-        <v>7051206</v>
+        <v>7051075</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -16851,12 +16851,12 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>På dimensionsavverkningsstubbe av tall i gammal gles barrblandskog</t>
+          <t>Födosökspår efter hästmyror</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16871,22 +16871,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>124447855</v>
+        <v>124462400</v>
       </c>
       <c r="B140" t="n">
-        <v>79920</v>
+        <v>74901</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16895,41 +16895,41 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>461216</v>
+        <v>460862</v>
       </c>
       <c r="R140" t="n">
-        <v>7050415</v>
+        <v>7051207</v>
       </c>
       <c r="S140" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16968,12 +16968,12 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>På bark på död stam av jolster i fuktig gammal granskog vid bäck</t>
+          <t>På gran ca 25 cm i diameter i gammal gles barrblandskog på blockrik mark</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16988,22 +16988,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>124459044</v>
+        <v>124452335</v>
       </c>
       <c r="B141" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -17012,38 +17012,38 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>460900</v>
+        <v>461106</v>
       </c>
       <c r="R141" t="n">
-        <v>7051032</v>
+        <v>7050697</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17075,7 +17075,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -17085,12 +17085,12 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter</t>
+          <t>På bark på stam av levande gammal grov sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17105,22 +17105,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>124462400</v>
+        <v>124452305</v>
       </c>
       <c r="B142" t="n">
-        <v>74901</v>
+        <v>79926</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -17129,38 +17129,38 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>460862</v>
+        <v>461106</v>
       </c>
       <c r="R142" t="n">
-        <v>7051207</v>
+        <v>7050697</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17192,7 +17192,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -17202,12 +17202,12 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter i gammal gles barrblandskog på blockrik mark</t>
+          <t>På bark på stam av levande gammal grov sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17222,22 +17222,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>124452335</v>
+        <v>124452111</v>
       </c>
       <c r="B143" t="n">
-        <v>79920</v>
+        <v>79826</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -17250,21 +17250,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6462</v>
+        <v>6457</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -17274,10 +17274,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>461106</v>
+        <v>461089</v>
       </c>
       <c r="R143" t="n">
-        <v>7050697</v>
+        <v>7050682</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17309,7 +17309,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -17319,12 +17319,12 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal grov sälg i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17344,17 +17344,17 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>124452305</v>
+        <v>124454161</v>
       </c>
       <c r="B144" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -17363,20 +17363,20 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -17387,14 +17387,14 @@
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>461106</v>
+        <v>461010</v>
       </c>
       <c r="R144" t="n">
-        <v>7050697</v>
+        <v>7050791</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17426,7 +17426,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal grov sälg i gammal granskog</t>
+          <t>Ett tiotal bålar på en gran</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17456,22 +17456,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>124452111</v>
+        <v>124459044</v>
       </c>
       <c r="B145" t="n">
-        <v>79826</v>
+        <v>74901</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -17480,38 +17480,38 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6457</v>
+        <v>6440</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>461089</v>
+        <v>460900</v>
       </c>
       <c r="R145" t="n">
-        <v>7050682</v>
+        <v>7051032</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17543,7 +17543,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -17553,12 +17553,12 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17573,12 +17573,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
@@ -19471,10 +19471,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>124452995</v>
+        <v>124447135</v>
       </c>
       <c r="B162" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -19487,21 +19487,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -19511,10 +19511,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>461058</v>
+        <v>461248</v>
       </c>
       <c r="R162" t="n">
-        <v>7050701</v>
+        <v>7050401</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19546,7 +19546,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -19556,12 +19556,12 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19588,7 +19588,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>124454733</v>
+        <v>124464548</v>
       </c>
       <c r="B163" t="n">
         <v>77743</v>
@@ -19628,10 +19628,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>460963</v>
+        <v>460857</v>
       </c>
       <c r="R163" t="n">
-        <v>7050824</v>
+        <v>7051101</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i granskog på fuktig mark</t>
+          <t>På senvuxen gran ca 15 cm i diameter I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19705,10 +19705,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>124462884</v>
+        <v>124452995</v>
       </c>
       <c r="B164" t="n">
-        <v>78547</v>
+        <v>91026</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -19721,34 +19721,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>228912</v>
+        <v>1204</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>460813</v>
+        <v>461058</v>
       </c>
       <c r="R164" t="n">
-        <v>7051241</v>
+        <v>7050701</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -19790,12 +19790,12 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>På kol på bränd högstubbe av tall ca 35 cm i diameter och 2,5 m hög i äldre barrblandskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19810,22 +19810,22 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>124460214</v>
+        <v>124454733</v>
       </c>
       <c r="B165" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -19838,21 +19838,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -19862,10 +19862,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>460862</v>
+        <v>460963</v>
       </c>
       <c r="R165" t="n">
-        <v>7051148</v>
+        <v>7050824</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19897,7 +19897,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19907,12 +19907,12 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Ett 30-tal bålar bålar på gammal gran ca 35 cm i diameter vid källa</t>
+          <t>På gran ca 35 cm i diameter i granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19939,7 +19939,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>124458954</v>
+        <v>124460214</v>
       </c>
       <c r="B166" t="n">
         <v>78810</v>
@@ -19979,10 +19979,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>460891</v>
+        <v>460862</v>
       </c>
       <c r="R166" t="n">
-        <v>7051023</v>
+        <v>7051148</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -20014,7 +20014,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -20024,12 +20024,12 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Ett 30-tal bålar på 3 granar</t>
+          <t>Ett 30-tal bålar bålar på gammal gran ca 35 cm i diameter vid källa</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -20056,10 +20056,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>124464548</v>
+        <v>124454537</v>
       </c>
       <c r="B167" t="n">
-        <v>77743</v>
+        <v>96985</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -20068,38 +20068,38 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>228579</v>
+        <v>221941</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>460857</v>
+        <v>460968</v>
       </c>
       <c r="R167" t="n">
-        <v>7051101</v>
+        <v>7050710</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -20131,7 +20131,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -20141,12 +20141,12 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>På senvuxen gran ca 15 cm i diameter I gammal barrblandskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20161,22 +20161,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>124449387</v>
+        <v>124458954</v>
       </c>
       <c r="B168" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -20189,34 +20189,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>461132</v>
+        <v>460891</v>
       </c>
       <c r="R168" t="n">
-        <v>7050550</v>
+        <v>7051023</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -20248,7 +20248,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -20258,7 +20258,12 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Ett 30-tal bålar på 3 granar</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -20285,10 +20290,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>124447135</v>
+        <v>124449387</v>
       </c>
       <c r="B169" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -20301,21 +20306,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -20325,10 +20330,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>461248</v>
+        <v>461132</v>
       </c>
       <c r="R169" t="n">
-        <v>7050401</v>
+        <v>7050550</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -20360,7 +20365,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -20370,12 +20375,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>10:12</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20390,22 +20390,22 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>124454537</v>
+        <v>124462884</v>
       </c>
       <c r="B170" t="n">
-        <v>96985</v>
+        <v>78547</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -20414,38 +20414,38 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>221941</v>
+        <v>228912</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>460968</v>
+        <v>460813</v>
       </c>
       <c r="R170" t="n">
-        <v>7050710</v>
+        <v>7051241</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -20487,12 +20487,12 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På kol på bränd högstubbe av tall ca 35 cm i diameter och 2,5 m hög i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -20507,12 +20507,12 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>

--- a/artfynd/A 12489-2025 artfynd.xlsx
+++ b/artfynd/A 12489-2025 artfynd.xlsx
@@ -1634,10 +1634,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124465595</v>
+        <v>124452779</v>
       </c>
       <c r="B10" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1650,21 +1650,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460928</v>
+        <v>461058</v>
       </c>
       <c r="R10" t="n">
-        <v>7050686</v>
+        <v>7050704</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter</t>
+          <t>Ett tiotal bålar på  en gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1751,10 +1751,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124452176</v>
+        <v>124451806</v>
       </c>
       <c r="B11" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1767,21 +1767,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1791,10 +1791,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461093</v>
+        <v>461113</v>
       </c>
       <c r="R11" t="n">
-        <v>7050684</v>
+        <v>7050637</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre granskog med inslag av björk och tall</t>
+          <t>På gra ca 35 cm i diameter i äldre granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1868,10 +1868,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124447843</v>
+        <v>124454920</v>
       </c>
       <c r="B12" t="n">
-        <v>74901</v>
+        <v>79927</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1880,25 +1880,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461226</v>
+        <v>460974</v>
       </c>
       <c r="R12" t="n">
-        <v>7050425</v>
+        <v>7050773</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran ca 40 cm i diameter i äldre granskog</t>
+          <t>På döda grankvistar påverkade av krondropp från gammal sälg i granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1973,22 +1973,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124447955</v>
+        <v>124447843</v>
       </c>
       <c r="B13" t="n">
-        <v>95335</v>
+        <v>74901</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1997,25 +1997,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461213</v>
+        <v>461226</v>
       </c>
       <c r="R13" t="n">
         <v>7050425</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På fuktig mark vid bäck i gammal granskog</t>
+          <t>På gran ca 40 cm i diameter i äldre granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2090,22 +2090,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124452779</v>
+        <v>124447955</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>95335</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2114,38 +2114,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461058</v>
+        <v>461213</v>
       </c>
       <c r="R14" t="n">
-        <v>7050704</v>
+        <v>7050425</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ett tiotal bålar på  en gran</t>
+          <t>På fuktig mark vid bäck i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2207,22 +2207,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124451806</v>
+        <v>124451344</v>
       </c>
       <c r="B15" t="n">
-        <v>74901</v>
+        <v>77753</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2235,34 +2235,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461113</v>
+        <v>461120</v>
       </c>
       <c r="R15" t="n">
-        <v>7050637</v>
+        <v>7050636</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2304,12 +2304,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gra ca 35 cm i diameter i äldre granskog</t>
+          <t>På undersidan av gren på senvuxen gran ca 16 cm i diameter, intill bäck</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2336,10 +2336,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124454920</v>
+        <v>124452642</v>
       </c>
       <c r="B16" t="n">
-        <v>79927</v>
+        <v>100279</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2352,34 +2352,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460974</v>
+        <v>461064</v>
       </c>
       <c r="R16" t="n">
-        <v>7050773</v>
+        <v>7050693</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2421,12 +2421,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På döda grankvistar påverkade av krondropp från gammal sälg i granskog</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2441,22 +2436,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124451344</v>
+        <v>124465595</v>
       </c>
       <c r="B17" t="n">
-        <v>77753</v>
+        <v>77743</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2469,34 +2464,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>314</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461120</v>
+        <v>460928</v>
       </c>
       <c r="R17" t="n">
-        <v>7050636</v>
+        <v>7050686</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2528,7 +2523,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2538,12 +2533,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På undersidan av gren på senvuxen gran ca 16 cm i diameter, intill bäck</t>
+          <t>På gran ca 35 cm i diameter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2570,10 +2565,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124452642</v>
+        <v>124452176</v>
       </c>
       <c r="B18" t="n">
-        <v>100279</v>
+        <v>77743</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2582,25 +2577,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2610,10 +2605,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461064</v>
+        <v>461093</v>
       </c>
       <c r="R18" t="n">
-        <v>7050693</v>
+        <v>7050684</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2645,7 +2640,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2655,7 +2650,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På gran ca 35 cm i diameter i äldre granskog med inslag av björk och tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3501,10 +3501,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124450918</v>
+        <v>124464583</v>
       </c>
       <c r="B26" t="n">
-        <v>79927</v>
+        <v>57529</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3513,38 +3513,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461131</v>
+        <v>460856</v>
       </c>
       <c r="R26" t="n">
-        <v>7050604</v>
+        <v>7051060</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3576,7 +3581,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3586,12 +3591,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På högstubbe av gråal ca 1 m från en bäck</t>
+          <t>Födosökshack efter hästmyror på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3606,22 +3611,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124453753</v>
+        <v>124465641</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>97185</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3630,41 +3635,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220686</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460993</v>
+        <v>460931</v>
       </c>
       <c r="R27" t="n">
-        <v>7050667</v>
+        <v>7050680</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3693,7 +3698,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3703,12 +3708,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gamla granar vid bäck i gammal granskog</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3723,22 +3723,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124458121</v>
+        <v>124450918</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3747,38 +3747,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>460890</v>
+        <v>461131</v>
       </c>
       <c r="R28" t="n">
-        <v>7050973</v>
+        <v>7050604</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ett 30-tal bålar på en gran</t>
+          <t>På högstubbe av gråal ca 1 m från en bäck</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3852,10 +3852,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124452111</v>
+        <v>124453753</v>
       </c>
       <c r="B29" t="n">
-        <v>79826</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3864,25 +3864,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461089</v>
+        <v>460993</v>
       </c>
       <c r="R29" t="n">
-        <v>7050682</v>
+        <v>7050667</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På gamla granar vid bäck i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3969,10 +3969,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124464945</v>
+        <v>124458121</v>
       </c>
       <c r="B30" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3985,21 +3985,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4009,10 +4009,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460854</v>
+        <v>460890</v>
       </c>
       <c r="R30" t="n">
-        <v>7050992</v>
+        <v>7050973</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter ca 7 m från bäck i gammal granskog</t>
+          <t>Ett 30-tal bålar på en gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4086,10 +4086,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124464583</v>
+        <v>124452111</v>
       </c>
       <c r="B31" t="n">
-        <v>57529</v>
+        <v>79826</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4098,43 +4098,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6457</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460856</v>
+        <v>461089</v>
       </c>
       <c r="R31" t="n">
-        <v>7051060</v>
+        <v>7050682</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4166,7 +4161,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4176,12 +4171,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Födosökshack efter hästmyror på gammal levande gran i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4208,10 +4203,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124457598</v>
+        <v>124464945</v>
       </c>
       <c r="B32" t="n">
-        <v>79851</v>
+        <v>74901</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4220,38 +4215,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229497</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460871</v>
+        <v>460854</v>
       </c>
       <c r="R32" t="n">
-        <v>7050927</v>
+        <v>7050992</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4283,7 +4278,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4293,12 +4288,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal död sälg i gammal granskog</t>
+          <t>På gran ca 35 cm i diameter ca 7 m från bäck i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4313,22 +4308,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124465641</v>
+        <v>124448755</v>
       </c>
       <c r="B33" t="n">
-        <v>97185</v>
+        <v>77743</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4337,41 +4332,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220686</v>
+        <v>228579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460931</v>
+        <v>461206</v>
       </c>
       <c r="R33" t="n">
-        <v>7050680</v>
+        <v>7050483</v>
       </c>
       <c r="S33" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4400,7 +4395,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4410,7 +4405,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal grov gran i kanten av gammal granskog nära bäck</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4425,22 +4425,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124447712</v>
+        <v>124447872</v>
       </c>
       <c r="B34" t="n">
-        <v>74713</v>
+        <v>77743</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4449,25 +4449,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6428</v>
+        <v>228579</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461235</v>
+        <v>461229</v>
       </c>
       <c r="R34" t="n">
-        <v>7050407</v>
+        <v>7050409</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre granskog på frisk-fuktig mark</t>
+          <t>På gran ca 40 cm i diameter i äldre granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4554,10 +4554,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124448755</v>
+        <v>124457598</v>
       </c>
       <c r="B35" t="n">
-        <v>77743</v>
+        <v>79851</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4566,25 +4566,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228579</v>
+        <v>229497</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4594,10 +4594,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461206</v>
+        <v>460871</v>
       </c>
       <c r="R35" t="n">
-        <v>7050483</v>
+        <v>7050927</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal grov gran i kanten av gammal granskog nära bäck</t>
+          <t>På gammal död sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4671,7 +4671,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124447872</v>
+        <v>124460183</v>
       </c>
       <c r="B36" t="n">
         <v>77743</v>
@@ -4707,14 +4707,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461229</v>
+        <v>460867</v>
       </c>
       <c r="R36" t="n">
-        <v>7050409</v>
+        <v>7051147</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gran ca 40 cm i diameter i äldre granskog</t>
+          <t>På bark på stam av levande gammal gran (ca 180 år gammal) i gammal granskog i fuktig sänka</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4776,22 +4776,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124460183</v>
+        <v>124447712</v>
       </c>
       <c r="B37" t="n">
-        <v>77743</v>
+        <v>74713</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4800,38 +4800,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228579</v>
+        <v>6428</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460867</v>
+        <v>461235</v>
       </c>
       <c r="R37" t="n">
-        <v>7051147</v>
+        <v>7050407</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (ca 180 år gammal) i gammal granskog i fuktig sänka</t>
+          <t>På gran ca 35 cm i diameter i äldre granskog på frisk-fuktig mark</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4893,12 +4893,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -6098,10 +6098,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124452524</v>
+        <v>124447855</v>
       </c>
       <c r="B48" t="n">
-        <v>79066</v>
+        <v>79920</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6114,21 +6114,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6459</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6138,13 +6138,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461106</v>
+        <v>461216</v>
       </c>
       <c r="R48" t="n">
-        <v>7050697</v>
+        <v>7050415</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På bark på död stam av jolster i fuktig gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6208,17 +6208,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124462439</v>
+        <v>124452524</v>
       </c>
       <c r="B49" t="n">
-        <v>79428</v>
+        <v>79066</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6227,38 +6227,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6459</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>460848</v>
+        <v>461106</v>
       </c>
       <c r="R49" t="n">
-        <v>7051206</v>
+        <v>7050697</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6300,12 +6300,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På dimensionsavverkningsstubbe av tall i gammal gles barrblandskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6320,19 +6320,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124461212</v>
+        <v>124462439</v>
       </c>
       <c r="B50" t="n">
         <v>79428</v>
@@ -6372,10 +6372,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>460856</v>
+        <v>460848</v>
       </c>
       <c r="R50" t="n">
-        <v>7051188</v>
+        <v>7051206</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På ved på gammal dimensionsavverkningsstubbe ca 35 cm i diameter och 1,3 meter hög. I öppen gles skog med gran, tall och björk på blockrik mark</t>
+          <t>På dimensionsavverkningsstubbe av tall i gammal gles barrblandskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6449,10 +6449,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124466958</v>
+        <v>124461212</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6465,43 +6465,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461083</v>
+        <v>460856</v>
       </c>
       <c r="R51" t="n">
-        <v>7050465</v>
+        <v>7051188</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6533,7 +6524,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6543,12 +6534,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På ved på gammal dimensionsavverkningsstubbe ca 35 cm i diameter och 1,3 meter hög. I öppen gles skog med gran, tall och björk på blockrik mark</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6563,22 +6554,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124447855</v>
+        <v>124466958</v>
       </c>
       <c r="B52" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6587,41 +6578,50 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461216</v>
+        <v>461083</v>
       </c>
       <c r="R52" t="n">
-        <v>7050415</v>
+        <v>7050465</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På bark på död stam av jolster i fuktig gammal granskog vid bäck</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -11021,10 +11021,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124451649</v>
+        <v>124458734</v>
       </c>
       <c r="B90" t="n">
-        <v>91026</v>
+        <v>56714</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11037,37 +11037,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1204</v>
+        <v>102612</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461108</v>
+        <v>460884</v>
       </c>
       <c r="R90" t="n">
-        <v>7050663</v>
+        <v>7050999</v>
       </c>
       <c r="S90" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11106,12 +11106,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog vid källflöde</t>
+          <t>1 spelande</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11126,22 +11126,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124455518</v>
+        <v>124451649</v>
       </c>
       <c r="B91" t="n">
-        <v>91012</v>
+        <v>91026</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11154,21 +11154,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11178,13 +11178,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>460913</v>
+        <v>461108</v>
       </c>
       <c r="R91" t="n">
-        <v>7050818</v>
+        <v>7050663</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11223,12 +11223,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog på ås</t>
+          <t>På granlåga i gammal granskog vid källflöde</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11248,14 +11248,14 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124459560</v>
+        <v>124455518</v>
       </c>
       <c r="B92" t="n">
         <v>91012</v>
@@ -11291,14 +11291,14 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>460899</v>
+        <v>460913</v>
       </c>
       <c r="R92" t="n">
-        <v>7051069</v>
+        <v>7050818</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På granlåga ca 35 cm i diameter, ligger över en bäck i en liten svacka/ravin</t>
+          <t>På gammal granlåga i gammal granskog på ås</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11360,22 +11360,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124453757</v>
+        <v>124459560</v>
       </c>
       <c r="B93" t="n">
-        <v>77743</v>
+        <v>91012</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11388,21 +11388,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11412,10 +11412,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>460989</v>
+        <v>460899</v>
       </c>
       <c r="R93" t="n">
-        <v>7050753</v>
+        <v>7051069</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11447,7 +11447,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På gran ca 45 cm i diameter</t>
+          <t>På granlåga ca 35 cm i diameter, ligger över en bäck i en liten svacka/ravin</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11489,10 +11489,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124464264</v>
+        <v>124457172</v>
       </c>
       <c r="B94" t="n">
-        <v>77743</v>
+        <v>100279</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11501,25 +11501,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228579</v>
+        <v>222498</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11529,10 +11529,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>460831</v>
+        <v>460933</v>
       </c>
       <c r="R94" t="n">
-        <v>7051167</v>
+        <v>7050887</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11564,7 +11564,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11574,12 +11574,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>På gran ca 30 cm i diameter i gammal barrblandskog</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11606,10 +11601,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124458734</v>
+        <v>124453757</v>
       </c>
       <c r="B95" t="n">
-        <v>56714</v>
+        <v>77743</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11622,21 +11617,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>102612</v>
+        <v>228579</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11646,13 +11641,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>460884</v>
+        <v>460989</v>
       </c>
       <c r="R95" t="n">
-        <v>7050999</v>
+        <v>7050753</v>
       </c>
       <c r="S95" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11681,7 +11676,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11691,12 +11686,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>1 spelande</t>
+          <t>På gran ca 45 cm i diameter</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11723,10 +11718,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124457172</v>
+        <v>124464264</v>
       </c>
       <c r="B96" t="n">
-        <v>100279</v>
+        <v>77743</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11735,25 +11730,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222498</v>
+        <v>228579</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11763,10 +11758,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>460933</v>
+        <v>460831</v>
       </c>
       <c r="R96" t="n">
-        <v>7050887</v>
+        <v>7051167</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11798,7 +11793,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11808,7 +11803,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>På gran ca 30 cm i diameter i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11835,10 +11835,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124452305</v>
+        <v>124447061</v>
       </c>
       <c r="B97" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11847,20 +11847,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -11875,10 +11875,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>461106</v>
+        <v>461254</v>
       </c>
       <c r="R97" t="n">
-        <v>7050697</v>
+        <v>7050397</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal grov sälg i gammal granskog</t>
+          <t>På gammal gran i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11945,17 +11945,17 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124451374</v>
+        <v>124452305</v>
       </c>
       <c r="B98" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11964,20 +11964,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -11992,13 +11992,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>461141</v>
+        <v>461106</v>
       </c>
       <c r="R98" t="n">
-        <v>7050660</v>
+        <v>7050697</v>
       </c>
       <c r="S98" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12037,12 +12037,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog vid källflöde</t>
+          <t>På bark på stam av levande gammal grov sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12062,17 +12062,17 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124454121</v>
+        <v>124451374</v>
       </c>
       <c r="B99" t="n">
-        <v>91950</v>
+        <v>78810</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12081,25 +12081,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -12109,13 +12109,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>461008</v>
+        <v>461141</v>
       </c>
       <c r="R99" t="n">
-        <v>7050615</v>
+        <v>7050660</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12154,12 +12154,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>På marken i bäckdråg  med gammal granskog med rikligt med död ved</t>
+          <t>På gammal gran i gammal granskog vid källflöde</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12179,17 +12179,17 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124452903</v>
+        <v>124454121</v>
       </c>
       <c r="B100" t="n">
-        <v>74901</v>
+        <v>91950</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12198,38 +12198,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6440</v>
+        <v>4769</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>461060</v>
+        <v>461008</v>
       </c>
       <c r="R100" t="n">
-        <v>7050712</v>
+        <v>7050615</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12271,12 +12271,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>På gran ca 30 cm i diameter I äldre granskog</t>
+          <t>På marken i bäckdråg  med gammal granskog med rikligt med död ved</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12291,22 +12291,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124460214</v>
+        <v>124452903</v>
       </c>
       <c r="B101" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12319,21 +12319,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12343,10 +12343,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>460862</v>
+        <v>461060</v>
       </c>
       <c r="R101" t="n">
-        <v>7051148</v>
+        <v>7050712</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Ett 30-tal bålar bålar på gammal gran ca 35 cm i diameter vid källa</t>
+          <t>På gran ca 30 cm i diameter I äldre granskog</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12420,10 +12420,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124464738</v>
+        <v>124460214</v>
       </c>
       <c r="B102" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12436,21 +12436,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12460,10 +12460,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>460836</v>
+        <v>460862</v>
       </c>
       <c r="R102" t="n">
-        <v>7051050</v>
+        <v>7051148</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12495,7 +12495,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12505,12 +12505,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>På gran ca 30 cm i diameter</t>
+          <t>Ett 30-tal bålar bålar på gammal gran ca 35 cm i diameter vid källa</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12537,10 +12537,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124458954</v>
+        <v>124464738</v>
       </c>
       <c r="B103" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12553,21 +12553,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12577,10 +12577,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>460891</v>
+        <v>460836</v>
       </c>
       <c r="R103" t="n">
-        <v>7051023</v>
+        <v>7051050</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12612,7 +12612,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12622,12 +12622,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Ett 30-tal bålar på 3 granar</t>
+          <t>På gran ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12654,10 +12654,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124454282</v>
+        <v>124458954</v>
       </c>
       <c r="B104" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12670,21 +12670,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12694,10 +12694,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461015</v>
+        <v>460891</v>
       </c>
       <c r="R104" t="n">
-        <v>7050800</v>
+        <v>7051023</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12739,12 +12739,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>På gran ca 30 cm i diameter</t>
+          <t>Ett 30-tal bålar på 3 granar</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12771,10 +12771,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124461083</v>
+        <v>124454282</v>
       </c>
       <c r="B105" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12787,34 +12787,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>460894</v>
+        <v>461015</v>
       </c>
       <c r="R105" t="n">
-        <v>7051182</v>
+        <v>7050800</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12846,7 +12846,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12856,12 +12856,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall i gammal tallskog på stenskravelmark</t>
+          <t>På gran ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12876,22 +12876,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124458517</v>
+        <v>124461083</v>
       </c>
       <c r="B106" t="n">
-        <v>79892</v>
+        <v>79428</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12904,34 +12904,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>460887</v>
+        <v>460894</v>
       </c>
       <c r="R106" t="n">
-        <v>7051004</v>
+        <v>7051182</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12973,12 +12973,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>På sälg ca 45 cm i diameter</t>
+          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall i gammal tallskog på stenskravelmark</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12993,22 +12993,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124457612</v>
+        <v>124458517</v>
       </c>
       <c r="B107" t="n">
-        <v>78891</v>
+        <v>79892</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13021,21 +13021,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>283</v>
+        <v>2081</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -13045,10 +13045,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>460898</v>
+        <v>460887</v>
       </c>
       <c r="R107" t="n">
-        <v>7050927</v>
+        <v>7051004</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13080,7 +13080,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>På kvist av gran ca 3 cm i diameter</t>
+          <t>På sälg ca 45 cm i diameter</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13122,10 +13122,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124456509</v>
+        <v>124457612</v>
       </c>
       <c r="B108" t="n">
-        <v>57883</v>
+        <v>78891</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13134,47 +13134,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103015</v>
+        <v>283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>460910</v>
+        <v>460898</v>
       </c>
       <c r="R108" t="n">
-        <v>7050839</v>
+        <v>7050927</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13206,7 +13197,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13216,12 +13207,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På kvist av gran ca 3 cm i diameter</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13236,22 +13227,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124459297</v>
+        <v>124456509</v>
       </c>
       <c r="B109" t="n">
-        <v>105102</v>
+        <v>57883</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13264,34 +13255,43 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221725</v>
+        <v>103015</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>460876</v>
+        <v>460910</v>
       </c>
       <c r="R109" t="n">
-        <v>7051057</v>
+        <v>7050839</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13323,7 +13323,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13333,12 +13333,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>På marken vid bäck i gammal granskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13365,10 +13365,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124459487</v>
+        <v>124459297</v>
       </c>
       <c r="B110" t="n">
-        <v>77743</v>
+        <v>105102</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13377,38 +13377,38 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228579</v>
+        <v>221725</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>460884</v>
+        <v>460876</v>
       </c>
       <c r="R110" t="n">
-        <v>7051067</v>
+        <v>7051057</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13440,7 +13440,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13450,12 +13450,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>På gran ca 40 cm i diameter</t>
+          <t>På marken vid bäck i gammal granskog</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13470,22 +13470,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124463287</v>
+        <v>124459487</v>
       </c>
       <c r="B111" t="n">
-        <v>78547</v>
+        <v>77743</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13498,21 +13498,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>228579</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -13522,10 +13522,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>460818</v>
+        <v>460884</v>
       </c>
       <c r="R111" t="n">
-        <v>7051226</v>
+        <v>7051067</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>På bränd högstubbe av tall ca 20 cm i diameter och 4 meter hög i gammal barrblandskog</t>
+          <t>På gran ca 40 cm i diameter</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13599,10 +13599,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124447061</v>
+        <v>124463287</v>
       </c>
       <c r="B112" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13615,34 +13615,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>461254</v>
+        <v>460818</v>
       </c>
       <c r="R112" t="n">
-        <v>7050397</v>
+        <v>7051226</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13674,7 +13674,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13684,12 +13684,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>På gammal gran i fuktig gammal granskog</t>
+          <t>På bränd högstubbe av tall ca 20 cm i diameter och 4 meter hög i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13704,12 +13704,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -14427,10 +14427,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124453365</v>
+        <v>124449191</v>
       </c>
       <c r="B119" t="n">
-        <v>100279</v>
+        <v>77743</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14439,38 +14439,38 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>222498</v>
+        <v>228579</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461017</v>
+        <v>461139</v>
       </c>
       <c r="R119" t="n">
-        <v>7050715</v>
+        <v>7050532</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14512,7 +14512,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>På gammal gran ca 35 cm i diameter i äldre granskog</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14539,10 +14544,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124449191</v>
+        <v>124463372</v>
       </c>
       <c r="B120" t="n">
-        <v>77743</v>
+        <v>79851</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14551,38 +14556,38 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228579</v>
+        <v>229497</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>461139</v>
+        <v>460809</v>
       </c>
       <c r="R120" t="n">
-        <v>7050532</v>
+        <v>7051220</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14614,7 +14619,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14624,12 +14629,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>På gammal gran ca 35 cm i diameter i äldre granskog</t>
+          <t>På döende sälg ca 45 cm i diameter I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14656,10 +14661,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124463372</v>
+        <v>124453365</v>
       </c>
       <c r="B121" t="n">
-        <v>79851</v>
+        <v>100279</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14672,21 +14677,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14696,10 +14701,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>460809</v>
+        <v>461017</v>
       </c>
       <c r="R121" t="n">
-        <v>7051220</v>
+        <v>7050715</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14731,7 +14736,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14741,12 +14746,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>På döende sälg ca 45 cm i diameter I gammal barrblandskog</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -17230,10 +17230,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>124456799</v>
+        <v>124458002</v>
       </c>
       <c r="B143" t="n">
-        <v>79851</v>
+        <v>74901</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -17242,25 +17242,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>229497</v>
+        <v>6440</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -17270,10 +17270,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>460948</v>
+        <v>460898</v>
       </c>
       <c r="R143" t="n">
-        <v>7050858</v>
+        <v>7050962</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17305,7 +17305,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -17315,12 +17315,12 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>På sälg ca 40 cm i diameter</t>
+          <t>På gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17347,10 +17347,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>124463955</v>
+        <v>124459788</v>
       </c>
       <c r="B144" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -17363,34 +17363,43 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>460891</v>
+        <v>460870</v>
       </c>
       <c r="R144" t="n">
-        <v>7051196</v>
+        <v>7051140</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17422,7 +17431,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -17432,12 +17441,12 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallhögstubbe i gammal barrblandskog på blockig mark i sydsluttning</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17464,10 +17473,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>124458002</v>
+        <v>124453534</v>
       </c>
       <c r="B145" t="n">
-        <v>74901</v>
+        <v>78891</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -17480,21 +17489,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6440</v>
+        <v>283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -17504,10 +17513,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>460898</v>
+        <v>461003</v>
       </c>
       <c r="R145" t="n">
-        <v>7050962</v>
+        <v>7050729</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17539,7 +17548,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -17549,12 +17558,12 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter</t>
+          <t>På kvist på levande liten gran ca 3 cm i diameter I granskog på frisk-fuktig mark</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17581,10 +17590,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>124459788</v>
+        <v>124464044</v>
       </c>
       <c r="B146" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -17597,43 +17606,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>460870</v>
+        <v>460886</v>
       </c>
       <c r="R146" t="n">
-        <v>7051140</v>
+        <v>7051158</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17665,7 +17665,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17675,12 +17675,12 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På ved på gammal tallrot på tallåga i gammal barrblandskog i sydsluttning</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17707,10 +17707,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>124453534</v>
+        <v>124456799</v>
       </c>
       <c r="B147" t="n">
-        <v>78891</v>
+        <v>79851</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -17719,25 +17719,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>283</v>
+        <v>229497</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17747,10 +17747,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>461003</v>
+        <v>460948</v>
       </c>
       <c r="R147" t="n">
-        <v>7050729</v>
+        <v>7050858</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17782,7 +17782,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17792,12 +17792,12 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>På kvist på levande liten gran ca 3 cm i diameter I granskog på frisk-fuktig mark</t>
+          <t>På sälg ca 40 cm i diameter</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17824,10 +17824,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>124464044</v>
+        <v>124463955</v>
       </c>
       <c r="B148" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17840,21 +17840,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17864,10 +17864,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>460886</v>
+        <v>460891</v>
       </c>
       <c r="R148" t="n">
-        <v>7051158</v>
+        <v>7051196</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17899,7 +17899,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17909,12 +17909,12 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>På ved på gammal tallrot på tallåga i gammal barrblandskog i sydsluttning</t>
+          <t>På kolad ved på gammal tallhögstubbe i gammal barrblandskog på blockig mark i sydsluttning</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17941,10 +17941,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>124448916</v>
+        <v>124452223</v>
       </c>
       <c r="B149" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17957,34 +17957,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>461180</v>
+        <v>461091</v>
       </c>
       <c r="R149" t="n">
-        <v>7050497</v>
+        <v>7050686</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -18016,7 +18016,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -18026,12 +18026,12 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal fuktig granskog</t>
+          <t>På gran ca 35 cm i diameter i äldre granskog med inslag av björk och tall</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18046,22 +18046,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>124452995</v>
+        <v>124457982</v>
       </c>
       <c r="B150" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -18074,34 +18074,43 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>461058</v>
+        <v>460959</v>
       </c>
       <c r="R150" t="n">
-        <v>7050701</v>
+        <v>7050954</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -18133,7 +18142,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -18143,12 +18152,12 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På döda granar i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18175,10 +18184,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>124452003</v>
+        <v>124460549</v>
       </c>
       <c r="B151" t="n">
-        <v>79851</v>
+        <v>78810</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -18187,38 +18196,38 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>461089</v>
+        <v>460858</v>
       </c>
       <c r="R151" t="n">
-        <v>7050682</v>
+        <v>7051170</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -18250,7 +18259,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -18260,12 +18269,12 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>Ett 15-tal bålar på en gran i äldre granskog med inslag av tall och björk, på blockrik mark</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18280,22 +18289,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124457471</v>
+        <v>124464120</v>
       </c>
       <c r="B152" t="n">
-        <v>77743</v>
+        <v>74713</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -18304,25 +18313,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>228579</v>
+        <v>6428</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18332,10 +18341,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>460904</v>
+        <v>460853</v>
       </c>
       <c r="R152" t="n">
-        <v>7050918</v>
+        <v>7051188</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18367,7 +18376,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -18377,12 +18386,12 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre granskog</t>
+          <t>På högstubbe av sälg ca 25 cm I diameter I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18409,10 +18418,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124454733</v>
+        <v>124459246</v>
       </c>
       <c r="B153" t="n">
-        <v>77743</v>
+        <v>91457</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -18421,38 +18430,38 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>228579</v>
+        <v>1209</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>460963</v>
+        <v>460886</v>
       </c>
       <c r="R153" t="n">
-        <v>7050824</v>
+        <v>7051067</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18484,7 +18493,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -18494,12 +18503,12 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i granskog på fuktig mark</t>
+          <t>Rikligt på granlåga i fuktigt läge ganska nära bäck, i gammal granskog</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18514,19 +18523,19 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124452223</v>
+        <v>124462400</v>
       </c>
       <c r="B154" t="n">
         <v>74901</v>
@@ -18566,10 +18575,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>461091</v>
+        <v>460862</v>
       </c>
       <c r="R154" t="n">
-        <v>7050686</v>
+        <v>7051207</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18601,7 +18610,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -18611,12 +18620,12 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre granskog med inslag av björk och tall</t>
+          <t>På gran ca 25 cm i diameter i gammal gles barrblandskog på blockrik mark</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18643,10 +18652,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124457982</v>
+        <v>124452995</v>
       </c>
       <c r="B155" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18659,43 +18668,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>460959</v>
+        <v>461058</v>
       </c>
       <c r="R155" t="n">
-        <v>7050954</v>
+        <v>7050701</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18727,7 +18727,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18737,12 +18737,12 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>På döda granar i gammal granskog på fuktig mark</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18769,10 +18769,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124460549</v>
+        <v>124449387</v>
       </c>
       <c r="B156" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18785,34 +18785,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>460858</v>
+        <v>461132</v>
       </c>
       <c r="R156" t="n">
-        <v>7051170</v>
+        <v>7050550</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18844,7 +18844,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18854,12 +18854,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Ett 15-tal bålar på en gran i äldre granskog med inslag av tall och björk, på blockrik mark</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18886,10 +18881,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>124464120</v>
+        <v>124452003</v>
       </c>
       <c r="B157" t="n">
-        <v>74713</v>
+        <v>79851</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18902,34 +18897,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6428</v>
+        <v>229497</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>460853</v>
+        <v>461089</v>
       </c>
       <c r="R157" t="n">
-        <v>7051188</v>
+        <v>7050682</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18961,7 +18956,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18971,12 +18966,12 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>På högstubbe av sälg ca 25 cm I diameter I gammal barrblandskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18991,22 +18986,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>124459246</v>
+        <v>124457471</v>
       </c>
       <c r="B158" t="n">
-        <v>91457</v>
+        <v>77743</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -19015,38 +19010,38 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1209</v>
+        <v>228579</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>460886</v>
+        <v>460904</v>
       </c>
       <c r="R158" t="n">
-        <v>7051067</v>
+        <v>7050918</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -19078,7 +19073,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -19088,12 +19083,12 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Rikligt på granlåga i fuktigt läge ganska nära bäck, i gammal granskog</t>
+          <t>På gran ca 35 cm i diameter i äldre granskog</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -19108,22 +19103,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>124462400</v>
+        <v>124454733</v>
       </c>
       <c r="B159" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -19136,21 +19131,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -19160,10 +19155,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>460862</v>
+        <v>460963</v>
       </c>
       <c r="R159" t="n">
-        <v>7051207</v>
+        <v>7050824</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19195,7 +19190,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19205,12 +19200,12 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter i gammal gles barrblandskog på blockrik mark</t>
+          <t>På gran ca 35 cm i diameter i granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19237,10 +19232,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>124449387</v>
+        <v>124448916</v>
       </c>
       <c r="B160" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -19253,21 +19248,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -19277,10 +19272,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>461132</v>
+        <v>461180</v>
       </c>
       <c r="R160" t="n">
-        <v>7050550</v>
+        <v>7050497</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19312,7 +19307,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19322,7 +19317,12 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19337,12 +19337,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>

--- a/artfynd/A 12489-2025 artfynd.xlsx
+++ b/artfynd/A 12489-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124462929</v>
+        <v>124451344</v>
       </c>
       <c r="B2" t="n">
-        <v>79428</v>
+        <v>77753</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460814</v>
+        <v>461120</v>
       </c>
       <c r="R2" t="n">
-        <v>7051237</v>
+        <v>7050636</v>
       </c>
       <c r="S2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På bränd högstubbe av tall i gammal barrblandskog</t>
+          <t>På undersidan av gren på senvuxen gran ca 16 cm i diameter, intill bäck</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124453753</v>
+        <v>124453534</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>78891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460993</v>
+        <v>461003</v>
       </c>
       <c r="R3" t="n">
-        <v>7050667</v>
+        <v>7050729</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gamla granar vid bäck i gammal granskog</t>
+          <t>På kvist på levande liten gran ca 3 cm i diameter I granskog på frisk-fuktig mark</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124457291</v>
+        <v>124462929</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460917</v>
+        <v>460814</v>
       </c>
       <c r="R4" t="n">
-        <v>7050904</v>
+        <v>7051237</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ett tiotal bålar på en gran</t>
+          <t>På bränd högstubbe av tall i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124466463</v>
+        <v>124453753</v>
       </c>
       <c r="B5" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,34 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460999</v>
+        <v>460993</v>
       </c>
       <c r="R5" t="n">
-        <v>7050500</v>
+        <v>7050667</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran ca 30 cm i diameter i äldre barrblandskog</t>
+          <t>På gamla granar vid bäck i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1131,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124451344</v>
+        <v>124457291</v>
       </c>
       <c r="B6" t="n">
-        <v>77753</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,34 +1159,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461120</v>
+        <v>460917</v>
       </c>
       <c r="R6" t="n">
-        <v>7050636</v>
+        <v>7050904</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På undersidan av gren på senvuxen gran ca 16 cm i diameter, intill bäck</t>
+          <t>Ett tiotal bålar på en gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124453534</v>
+        <v>124466463</v>
       </c>
       <c r="B7" t="n">
-        <v>78891</v>
+        <v>74901</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461003</v>
+        <v>460999</v>
       </c>
       <c r="R7" t="n">
-        <v>7050729</v>
+        <v>7050500</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På kvist på levande liten gran ca 3 cm i diameter I granskog på frisk-fuktig mark</t>
+          <t>På gran ca 30 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1728,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124457612</v>
+        <v>124447712</v>
       </c>
       <c r="B11" t="n">
-        <v>78891</v>
+        <v>74713</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,38 +1740,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>283</v>
+        <v>6428</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460898</v>
+        <v>461235</v>
       </c>
       <c r="R11" t="n">
-        <v>7050927</v>
+        <v>7050407</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,12 +1813,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På kvist av gran ca 3 cm i diameter</t>
+          <t>På gran ca 35 cm i diameter i äldre granskog på frisk-fuktig mark</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,7 +1845,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124454602</v>
+        <v>124457612</v>
       </c>
       <c r="B12" t="n">
         <v>78891</v>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460996</v>
+        <v>460898</v>
       </c>
       <c r="R12" t="n">
-        <v>7050828</v>
+        <v>7050927</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran med avbruten topp ca 6 cm i diameter i äldre granskog på frisk-fuktig mark</t>
+          <t>På kvist av gran ca 3 cm i diameter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124463955</v>
+        <v>124465980</v>
       </c>
       <c r="B13" t="n">
-        <v>78547</v>
+        <v>74901</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1978,34 +1978,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460891</v>
+        <v>460929</v>
       </c>
       <c r="R13" t="n">
-        <v>7051196</v>
+        <v>7050642</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallhögstubbe i gammal barrblandskog på blockig mark i sydsluttning</t>
+          <t>På gran 20 cm i diameter I äldre granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,22 +2067,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124450918</v>
+        <v>124454602</v>
       </c>
       <c r="B14" t="n">
-        <v>79927</v>
+        <v>78891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2091,38 +2091,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461131</v>
+        <v>460996</v>
       </c>
       <c r="R14" t="n">
-        <v>7050604</v>
+        <v>7050828</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På högstubbe av gråal ca 1 m från en bäck</t>
+          <t>På gran med avbruten topp ca 6 cm i diameter i äldre granskog på frisk-fuktig mark</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2196,10 +2196,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124451374</v>
+        <v>124450918</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2208,25 +2208,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2236,13 +2236,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461141</v>
+        <v>461131</v>
       </c>
       <c r="R15" t="n">
-        <v>7050660</v>
+        <v>7050604</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog vid källflöde</t>
+          <t>På högstubbe av gråal ca 1 m från en bäck</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2301,22 +2301,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124463308</v>
+        <v>124451374</v>
       </c>
       <c r="B16" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2329,37 +2329,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460818</v>
+        <v>461141</v>
       </c>
       <c r="R16" t="n">
-        <v>7051226</v>
+        <v>7050660</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bränd högstubbe av tall</t>
+          <t>På gammal gran i gammal granskog vid källflöde</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2418,19 +2418,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124462570</v>
+        <v>124463308</v>
       </c>
       <c r="B17" t="n">
         <v>79428</v>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460850</v>
+        <v>460818</v>
       </c>
       <c r="R17" t="n">
-        <v>7051224</v>
+        <v>7051226</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På dimensionsavverkningsstubbe av tall i gammal gles barrblandskog</t>
+          <t>På bränd högstubbe av tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2547,10 +2547,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124465980</v>
+        <v>124462570</v>
       </c>
       <c r="B18" t="n">
-        <v>74901</v>
+        <v>79428</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2563,21 +2563,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460929</v>
+        <v>460850</v>
       </c>
       <c r="R18" t="n">
-        <v>7050642</v>
+        <v>7051224</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran 20 cm i diameter I äldre granskog</t>
+          <t>På dimensionsavverkningsstubbe av tall i gammal gles barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2664,10 +2664,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124447712</v>
+        <v>124463955</v>
       </c>
       <c r="B19" t="n">
-        <v>74713</v>
+        <v>78547</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2676,38 +2676,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6428</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461235</v>
+        <v>460891</v>
       </c>
       <c r="R19" t="n">
-        <v>7050407</v>
+        <v>7051196</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre granskog på frisk-fuktig mark</t>
+          <t>På kolad ved på gammal tallhögstubbe i gammal barrblandskog på blockig mark i sydsluttning</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2769,12 +2769,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -6543,10 +6543,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124456787</v>
+        <v>124459788</v>
       </c>
       <c r="B52" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6555,20 +6555,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6576,17 +6576,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>460939</v>
+        <v>460870</v>
       </c>
       <c r="R52" t="n">
-        <v>7050867</v>
+        <v>7051140</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6618,7 +6627,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6628,12 +6637,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På sälg ca 40 cm i diameter</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6648,22 +6657,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124459788</v>
+        <v>124461083</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6676,43 +6685,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>460870</v>
+        <v>460894</v>
       </c>
       <c r="R53" t="n">
-        <v>7051140</v>
+        <v>7051182</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall i gammal tallskog på stenskravelmark</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6786,10 +6786,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124461083</v>
+        <v>124452233</v>
       </c>
       <c r="B54" t="n">
-        <v>79428</v>
+        <v>79892</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6802,37 +6802,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460894</v>
+        <v>461106</v>
       </c>
       <c r="R54" t="n">
-        <v>7051182</v>
+        <v>7050697</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall i gammal tallskog på stenskravelmark</t>
+          <t>På bark på stam av levande gammal grov sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6903,10 +6903,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124452233</v>
+        <v>124464583</v>
       </c>
       <c r="B55" t="n">
-        <v>79892</v>
+        <v>57529</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6919,37 +6919,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461106</v>
+        <v>460856</v>
       </c>
       <c r="R55" t="n">
-        <v>7050697</v>
+        <v>7051060</v>
       </c>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6978,7 +6983,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6988,12 +6993,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal grov sälg i gammal granskog</t>
+          <t>Födosökshack efter hästmyror på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7013,7 +7018,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7254,10 +7259,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124464583</v>
+        <v>124456787</v>
       </c>
       <c r="B58" t="n">
-        <v>57529</v>
+        <v>79926</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7266,43 +7271,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>460856</v>
+        <v>460939</v>
       </c>
       <c r="R58" t="n">
-        <v>7051060</v>
+        <v>7050867</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Födosökshack efter hästmyror på gammal levande gran i gammal granskog</t>
+          <t>På sälg ca 40 cm i diameter</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7364,12 +7364,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -8429,10 +8429,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124464120</v>
+        <v>124459017</v>
       </c>
       <c r="B68" t="n">
-        <v>74713</v>
+        <v>79920</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8445,34 +8445,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6428</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>460853</v>
+        <v>460902</v>
       </c>
       <c r="R68" t="n">
-        <v>7051188</v>
+        <v>7051049</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På högstubbe av sälg ca 25 cm I diameter I gammal barrblandskog</t>
+          <t>På gammal sälglåga i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8534,22 +8534,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124451835</v>
+        <v>124464357</v>
       </c>
       <c r="B69" t="n">
-        <v>90977</v>
+        <v>79926</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8562,34 +8562,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461102</v>
+        <v>460827</v>
       </c>
       <c r="R69" t="n">
-        <v>7050652</v>
+        <v>7051140</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8621,7 +8621,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog vid källflöde</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8651,22 +8651,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124461976</v>
+        <v>124457577</v>
       </c>
       <c r="B70" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8679,43 +8679,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>460859</v>
+        <v>460871</v>
       </c>
       <c r="R70" t="n">
-        <v>7051203</v>
+        <v>7050927</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8747,7 +8738,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8757,12 +8748,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>I gles gammal barrblandskog</t>
+          <t>På död gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8777,22 +8768,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124452642</v>
+        <v>124467315</v>
       </c>
       <c r="B71" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8801,38 +8792,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461064</v>
+        <v>461165</v>
       </c>
       <c r="R71" t="n">
-        <v>7050693</v>
+        <v>7050419</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8864,7 +8855,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8874,7 +8865,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På gammal gran (ca 170 år) i gammal granskog vid sumpmyr</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8889,22 +8885,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124460812</v>
+        <v>124464738</v>
       </c>
       <c r="B72" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8917,21 +8913,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8941,10 +8937,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>460858</v>
+        <v>460836</v>
       </c>
       <c r="R72" t="n">
-        <v>7051170</v>
+        <v>7051050</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8976,7 +8972,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8986,12 +8982,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På gran ca 30 cm i diameter i gles granskog med inslag av tall och björk, blockrik</t>
+          <t>På gran ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9018,10 +9014,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124459017</v>
+        <v>124464120</v>
       </c>
       <c r="B73" t="n">
-        <v>79920</v>
+        <v>74713</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9034,34 +9030,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>6428</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>460902</v>
+        <v>460853</v>
       </c>
       <c r="R73" t="n">
-        <v>7051049</v>
+        <v>7051188</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9093,7 +9089,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9103,12 +9099,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På gammal sälglåga i kanten av gammal granskog</t>
+          <t>På högstubbe av sälg ca 25 cm I diameter I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9123,22 +9119,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124464357</v>
+        <v>124461976</v>
       </c>
       <c r="B74" t="n">
-        <v>79926</v>
+        <v>57666</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9147,38 +9143,47 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6463</v>
+        <v>103021</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>460827</v>
+        <v>460859</v>
       </c>
       <c r="R74" t="n">
-        <v>7051140</v>
+        <v>7051203</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9210,7 +9215,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9220,12 +9225,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>I gles gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9252,10 +9257,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124457577</v>
+        <v>124452642</v>
       </c>
       <c r="B75" t="n">
-        <v>79891</v>
+        <v>100279</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9264,38 +9269,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>460871</v>
+        <v>461064</v>
       </c>
       <c r="R75" t="n">
-        <v>7050927</v>
+        <v>7050693</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9327,7 +9332,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9337,12 +9342,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På död gammal sälg i gammal granskog</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9357,22 +9357,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124467315</v>
+        <v>124451835</v>
       </c>
       <c r="B76" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9381,38 +9381,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461165</v>
+        <v>461102</v>
       </c>
       <c r="R76" t="n">
-        <v>7050419</v>
+        <v>7050652</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9454,12 +9454,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 170 år) i gammal granskog vid sumpmyr</t>
+          <t>På granlåga i gammal granskog vid källflöde</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9486,10 +9486,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124464738</v>
+        <v>124452995</v>
       </c>
       <c r="B77" t="n">
-        <v>74901</v>
+        <v>91026</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9502,34 +9502,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>460836</v>
+        <v>461058</v>
       </c>
       <c r="R77" t="n">
-        <v>7051050</v>
+        <v>7050701</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På gran ca 30 cm i diameter</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9591,22 +9591,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124452995</v>
+        <v>124460812</v>
       </c>
       <c r="B78" t="n">
-        <v>91026</v>
+        <v>77743</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9619,34 +9619,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1204</v>
+        <v>228579</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461058</v>
+        <v>460858</v>
       </c>
       <c r="R78" t="n">
-        <v>7050701</v>
+        <v>7051170</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På gran ca 30 cm i diameter i gles granskog med inslag av tall och björk, blockrik</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9708,12 +9708,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9954,10 +9954,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124463101</v>
+        <v>124458734</v>
       </c>
       <c r="B81" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9970,21 +9970,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9994,13 +9994,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>460803</v>
+        <v>460884</v>
       </c>
       <c r="R81" t="n">
-        <v>7051229</v>
+        <v>7050999</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ca 20 bålar på en gran i gammal barrblandskog</t>
+          <t>1 spelande</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10071,10 +10071,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124454282</v>
+        <v>124457598</v>
       </c>
       <c r="B82" t="n">
-        <v>74901</v>
+        <v>79851</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10083,38 +10083,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6440</v>
+        <v>229497</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>461015</v>
+        <v>460871</v>
       </c>
       <c r="R82" t="n">
-        <v>7050800</v>
+        <v>7050927</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10156,12 +10156,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På gran ca 30 cm i diameter</t>
+          <t>På gammal död sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10176,22 +10176,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124463409</v>
+        <v>124457081</v>
       </c>
       <c r="B83" t="n">
-        <v>91030</v>
+        <v>77743</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10204,21 +10204,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10228,10 +10228,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>460811</v>
+        <v>460936</v>
       </c>
       <c r="R83" t="n">
-        <v>7051224</v>
+        <v>7050880</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10273,12 +10273,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På högstubbe av gran</t>
+          <t>På gran ca 35 cm i diameter</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10305,7 +10305,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124454480</v>
+        <v>124463409</v>
       </c>
       <c r="B84" t="n">
         <v>91030</v>
@@ -10345,10 +10345,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461006</v>
+        <v>460811</v>
       </c>
       <c r="R84" t="n">
-        <v>7050820</v>
+        <v>7051224</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>På döende gran I äldre granskog på frisk-fuktig/fuktig mark. Även två bohål.</t>
+          <t>På högstubbe av gran</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10422,10 +10422,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124458734</v>
+        <v>124454480</v>
       </c>
       <c r="B85" t="n">
-        <v>56714</v>
+        <v>91030</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10438,21 +10438,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10462,13 +10462,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>460884</v>
+        <v>461006</v>
       </c>
       <c r="R85" t="n">
-        <v>7050999</v>
+        <v>7050820</v>
       </c>
       <c r="S85" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>1 spelande</t>
+          <t>På döende gran I äldre granskog på frisk-fuktig/fuktig mark. Även två bohål.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10656,10 +10656,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124457598</v>
+        <v>124463101</v>
       </c>
       <c r="B87" t="n">
-        <v>79851</v>
+        <v>78810</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10668,38 +10668,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>460871</v>
+        <v>460803</v>
       </c>
       <c r="R87" t="n">
-        <v>7050927</v>
+        <v>7051229</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10731,7 +10731,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10741,12 +10741,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På gammal död sälg i gammal granskog</t>
+          <t>Ca 20 bålar på en gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10761,22 +10761,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124457081</v>
+        <v>124454282</v>
       </c>
       <c r="B88" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10789,21 +10789,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10813,10 +10813,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>460936</v>
+        <v>461015</v>
       </c>
       <c r="R88" t="n">
-        <v>7050880</v>
+        <v>7050800</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10848,7 +10848,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10858,12 +10858,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter</t>
+          <t>På gran ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10890,10 +10890,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124452335</v>
+        <v>124447843</v>
       </c>
       <c r="B89" t="n">
-        <v>79920</v>
+        <v>74901</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10902,25 +10902,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10930,10 +10930,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461106</v>
+        <v>461226</v>
       </c>
       <c r="R89" t="n">
-        <v>7050697</v>
+        <v>7050425</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10965,7 +10965,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10975,12 +10975,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal grov sälg i gammal granskog</t>
+          <t>På gran ca 40 cm i diameter i äldre granskog</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10995,22 +10995,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124447843</v>
+        <v>124452335</v>
       </c>
       <c r="B90" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11019,25 +11019,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -11047,10 +11047,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461226</v>
+        <v>461106</v>
       </c>
       <c r="R90" t="n">
-        <v>7050425</v>
+        <v>7050697</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På gran ca 40 cm i diameter i äldre granskog</t>
+          <t>På bark på stam av levande gammal grov sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11112,12 +11112,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -15709,10 +15709,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124449498</v>
+        <v>124459169</v>
       </c>
       <c r="B130" t="n">
-        <v>77743</v>
+        <v>91012</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15725,34 +15725,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>461115</v>
+        <v>460887</v>
       </c>
       <c r="R130" t="n">
-        <v>7050559</v>
+        <v>7051060</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15794,12 +15794,12 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>På gammal gran ca 20 cm I diameter I äldre granskog med tallinslag</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15814,22 +15814,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>124458130</v>
+        <v>124455106</v>
       </c>
       <c r="B131" t="n">
-        <v>79892</v>
+        <v>98101</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15838,41 +15838,55 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>460978</v>
+        <v>460928</v>
       </c>
       <c r="R131" t="n">
-        <v>7050963</v>
+        <v>7050799</v>
       </c>
       <c r="S131" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15901,7 +15915,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15911,12 +15925,12 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande sälg i gammal granskog på fuktig mark</t>
+          <t>37 plantor inom 0,5x0,5 meter, många små och unga plantor men även en vinterståndare. Intill gammal igenväxande fäbodstig.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15936,17 +15950,17 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>124458517</v>
+        <v>124453869</v>
       </c>
       <c r="B132" t="n">
-        <v>79892</v>
+        <v>80783</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15959,34 +15973,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2081</v>
+        <v>229436</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Halmgul örnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ochrolechia alboflavescens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Wulfen) Zahlbr.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>460887</v>
+        <v>461025</v>
       </c>
       <c r="R132" t="n">
-        <v>7051004</v>
+        <v>7050650</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -16018,7 +16032,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -16028,12 +16042,12 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>På sälg ca 45 cm i diameter</t>
+          <t>På bark på död gren på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16048,22 +16062,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>124459169</v>
+        <v>124452541</v>
       </c>
       <c r="B133" t="n">
-        <v>91012</v>
+        <v>77743</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -16076,34 +16090,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>460887</v>
+        <v>461068</v>
       </c>
       <c r="R133" t="n">
-        <v>7051060</v>
+        <v>7050690</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16135,7 +16149,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -16145,12 +16159,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gran ca 45 cm i diameter i äldre granskog</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16165,22 +16179,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>124455106</v>
+        <v>124449498</v>
       </c>
       <c r="B134" t="n">
-        <v>98101</v>
+        <v>77743</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16189,52 +16203,38 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>460928</v>
+        <v>461115</v>
       </c>
       <c r="R134" t="n">
-        <v>7050799</v>
+        <v>7050559</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16266,7 +16266,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -16276,12 +16276,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>37 plantor inom 0,5x0,5 meter, många små och unga plantor men även en vinterståndare. Intill gammal igenväxande fäbodstig.</t>
+          <t>På gammal gran ca 20 cm I diameter I äldre granskog med tallinslag</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16296,22 +16296,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124453869</v>
+        <v>124458130</v>
       </c>
       <c r="B135" t="n">
-        <v>80783</v>
+        <v>79892</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16324,21 +16324,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>229436</v>
+        <v>2081</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Halmgul örnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ochrolechia alboflavescens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Wulfen) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -16348,13 +16348,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>461025</v>
+        <v>460978</v>
       </c>
       <c r="R135" t="n">
-        <v>7050650</v>
+        <v>7050963</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -16393,12 +16393,12 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>På bark på död gren på gammal levande gran i gammal granskog</t>
+          <t>På bark vid basen av gammal levande sälg i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16425,10 +16425,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>124452541</v>
+        <v>124458517</v>
       </c>
       <c r="B136" t="n">
-        <v>77743</v>
+        <v>79892</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16441,21 +16441,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -16465,10 +16465,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>461068</v>
+        <v>460887</v>
       </c>
       <c r="R136" t="n">
-        <v>7050690</v>
+        <v>7051004</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>På gran ca 45 cm i diameter i äldre granskog</t>
+          <t>På sälg ca 45 cm i diameter</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -17712,10 +17712,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>124453554</v>
+        <v>124452223</v>
       </c>
       <c r="B147" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -17728,34 +17728,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>461012</v>
+        <v>461091</v>
       </c>
       <c r="R147" t="n">
-        <v>7050679</v>
+        <v>7050686</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17787,7 +17787,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17797,12 +17797,12 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>På granlåga i fuktigt läge vid bäckdråg, i gammal granskog</t>
+          <t>På gran ca 35 cm i diameter i äldre granskog med inslag av björk och tall</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17817,22 +17817,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>124459477</v>
+        <v>124452252</v>
       </c>
       <c r="B148" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17845,39 +17845,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>460890</v>
+        <v>461106</v>
       </c>
       <c r="R148" t="n">
-        <v>7051075</v>
+        <v>7050697</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17909,7 +17904,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17919,12 +17914,12 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Födosökspår efter hästmyror</t>
+          <t>På bark på stam av levande gammal grov sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17951,10 +17946,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>124464212</v>
+        <v>124452779</v>
       </c>
       <c r="B149" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17967,37 +17962,37 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>460841</v>
+        <v>461058</v>
       </c>
       <c r="R149" t="n">
-        <v>7051180</v>
+        <v>7050704</v>
       </c>
       <c r="S149" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -18026,7 +18021,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -18036,12 +18031,12 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallhögstubbe i gammal granskog</t>
+          <t>Ett tiotal bålar på  en gran</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18056,19 +18051,19 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>124447855</v>
+        <v>124459961</v>
       </c>
       <c r="B150" t="n">
         <v>79920</v>
@@ -18104,17 +18099,17 @@
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>461216</v>
+        <v>460864</v>
       </c>
       <c r="R150" t="n">
-        <v>7050415</v>
+        <v>7051145</v>
       </c>
       <c r="S150" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -18143,7 +18138,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -18153,12 +18148,12 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>På bark på död stam av jolster i fuktig gammal granskog vid bäck</t>
+          <t>På sälg ca 18 cm i diameter</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18173,22 +18168,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>124452223</v>
+        <v>124452111</v>
       </c>
       <c r="B151" t="n">
-        <v>74901</v>
+        <v>79826</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -18197,38 +18192,38 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6440</v>
+        <v>6457</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>461091</v>
+        <v>461089</v>
       </c>
       <c r="R151" t="n">
-        <v>7050686</v>
+        <v>7050682</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -18260,7 +18255,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -18270,12 +18265,12 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre granskog med inslag av björk och tall</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18290,22 +18285,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124452252</v>
+        <v>124460549</v>
       </c>
       <c r="B152" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -18318,34 +18313,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>461106</v>
+        <v>460858</v>
       </c>
       <c r="R152" t="n">
-        <v>7050697</v>
+        <v>7051170</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18377,7 +18372,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -18387,12 +18382,12 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal grov sälg i gammal granskog</t>
+          <t>Ett 15-tal bålar på en gran i äldre granskog med inslag av tall och björk, på blockrik mark</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18407,22 +18402,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124452779</v>
+        <v>124458601</v>
       </c>
       <c r="B153" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -18431,25 +18426,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -18459,10 +18454,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>461058</v>
+        <v>460890</v>
       </c>
       <c r="R153" t="n">
-        <v>7050704</v>
+        <v>7051009</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18494,7 +18489,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -18504,12 +18499,12 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Ett tiotal bålar på  en gran</t>
+          <t>På sälg ca 45 cm i diameter</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18536,10 +18531,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124459961</v>
+        <v>124466220</v>
       </c>
       <c r="B154" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -18548,25 +18543,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -18576,10 +18571,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>460864</v>
+        <v>460940</v>
       </c>
       <c r="R154" t="n">
-        <v>7051145</v>
+        <v>7050559</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18611,7 +18606,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -18621,12 +18616,12 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>På sälg ca 18 cm i diameter</t>
+          <t>På levande gran I äldre granskog</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18653,10 +18648,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124452111</v>
+        <v>124464212</v>
       </c>
       <c r="B155" t="n">
-        <v>79826</v>
+        <v>78547</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18665,41 +18660,41 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6457</v>
+        <v>228912</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>461089</v>
+        <v>460841</v>
       </c>
       <c r="R155" t="n">
-        <v>7050682</v>
+        <v>7051180</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18728,7 +18723,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18738,12 +18733,12 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På kolad ved på gammal tallhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18770,10 +18765,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124460549</v>
+        <v>124447855</v>
       </c>
       <c r="B156" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18782,41 +18777,41 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>460858</v>
+        <v>461216</v>
       </c>
       <c r="R156" t="n">
-        <v>7051170</v>
+        <v>7050415</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18845,7 +18840,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18855,12 +18850,12 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Ett 15-tal bålar på en gran i äldre granskog med inslag av tall och björk, på blockrik mark</t>
+          <t>På bark på död stam av jolster i fuktig gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18875,22 +18870,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>124458601</v>
+        <v>124453554</v>
       </c>
       <c r="B157" t="n">
-        <v>79920</v>
+        <v>91012</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18899,38 +18894,38 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>460890</v>
+        <v>461012</v>
       </c>
       <c r="R157" t="n">
-        <v>7051009</v>
+        <v>7050679</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18962,7 +18957,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18972,12 +18967,12 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>På sälg ca 45 cm i diameter</t>
+          <t>På granlåga i fuktigt läge vid bäckdråg, i gammal granskog</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18992,22 +18987,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>124466220</v>
+        <v>124459477</v>
       </c>
       <c r="B158" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -19020,34 +19015,39 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>460940</v>
+        <v>460890</v>
       </c>
       <c r="R158" t="n">
-        <v>7050559</v>
+        <v>7051075</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -19079,7 +19079,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -19089,12 +19089,12 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>På levande gran I äldre granskog</t>
+          <t>Födosökspår efter hästmyror</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -19109,22 +19109,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>124447135</v>
+        <v>124456604</v>
       </c>
       <c r="B159" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -19137,21 +19137,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -19161,10 +19161,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>461248</v>
+        <v>460930</v>
       </c>
       <c r="R159" t="n">
-        <v>7050401</v>
+        <v>7050842</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19196,7 +19196,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19206,12 +19206,12 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>Rikligt på gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19238,10 +19238,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>124459246</v>
+        <v>124451942</v>
       </c>
       <c r="B160" t="n">
-        <v>91457</v>
+        <v>79891</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -19250,41 +19250,41 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>460886</v>
+        <v>461096</v>
       </c>
       <c r="R160" t="n">
-        <v>7051067</v>
+        <v>7050682</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19323,12 +19323,12 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Rikligt på granlåga i fuktigt läge ganska nära bäck, i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19348,17 +19348,17 @@
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>124456604</v>
+        <v>124460160</v>
       </c>
       <c r="B161" t="n">
-        <v>79891</v>
+        <v>79919</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -19367,41 +19367,50 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>460930</v>
+        <v>460878</v>
       </c>
       <c r="R161" t="n">
-        <v>7050842</v>
+        <v>7051147</v>
       </c>
       <c r="S161" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -19430,7 +19439,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19440,12 +19449,12 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Rikligt på gammal sälg i gammal granskog</t>
+          <t>Rikligt på marken i fuktig sänka med rejält gammal granskog</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19472,10 +19481,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>124451942</v>
+        <v>124458002</v>
       </c>
       <c r="B162" t="n">
-        <v>79891</v>
+        <v>74901</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -19488,37 +19497,37 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>461096</v>
+        <v>460898</v>
       </c>
       <c r="R162" t="n">
-        <v>7050682</v>
+        <v>7050962</v>
       </c>
       <c r="S162" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -19547,7 +19556,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -19557,12 +19566,12 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19577,22 +19586,22 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>124460160</v>
+        <v>124459044</v>
       </c>
       <c r="B163" t="n">
-        <v>79919</v>
+        <v>74901</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -19601,50 +19610,41 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6461</v>
+        <v>6440</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>460878</v>
+        <v>460900</v>
       </c>
       <c r="R163" t="n">
-        <v>7051147</v>
+        <v>7051032</v>
       </c>
       <c r="S163" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -19683,12 +19683,12 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Rikligt på marken i fuktig sänka med rejält gammal granskog</t>
+          <t>På gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19703,22 +19703,22 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>124458002</v>
+        <v>124455549</v>
       </c>
       <c r="B164" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -19727,25 +19727,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -19755,10 +19755,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>460898</v>
+        <v>460935</v>
       </c>
       <c r="R164" t="n">
-        <v>7050962</v>
+        <v>7050779</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19790,7 +19790,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -19800,12 +19800,12 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter</t>
+          <t>På sälg ca 45 cm i diameter</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19832,10 +19832,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>124459044</v>
+        <v>124448758</v>
       </c>
       <c r="B165" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -19848,34 +19848,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>460900</v>
+        <v>461238</v>
       </c>
       <c r="R165" t="n">
-        <v>7051032</v>
+        <v>7050458</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19907,7 +19907,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19917,12 +19917,12 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter</t>
+          <t>På gran ca 35 cm i diameter i äldre granskog på frisk-fuktig mark</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19949,10 +19949,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>124455549</v>
+        <v>124449387</v>
       </c>
       <c r="B166" t="n">
-        <v>79920</v>
+        <v>77743</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19961,38 +19961,38 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6462</v>
+        <v>228579</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>460935</v>
+        <v>461132</v>
       </c>
       <c r="R166" t="n">
-        <v>7050779</v>
+        <v>7050550</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -20024,7 +20024,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -20034,12 +20034,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>På sälg ca 45 cm i diameter</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -20066,10 +20061,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>124448758</v>
+        <v>124459246</v>
       </c>
       <c r="B167" t="n">
-        <v>77743</v>
+        <v>91457</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -20078,38 +20073,38 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>228579</v>
+        <v>1209</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>461238</v>
+        <v>460886</v>
       </c>
       <c r="R167" t="n">
-        <v>7050458</v>
+        <v>7051067</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -20141,7 +20136,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -20151,12 +20146,12 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre granskog på frisk-fuktig mark</t>
+          <t>Rikligt på granlåga i fuktigt läge ganska nära bäck, i gammal granskog</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20171,22 +20166,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>124449387</v>
+        <v>124447135</v>
       </c>
       <c r="B168" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -20199,21 +20194,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -20223,10 +20218,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>461132</v>
+        <v>461248</v>
       </c>
       <c r="R168" t="n">
-        <v>7050550</v>
+        <v>7050401</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -20258,7 +20253,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -20268,7 +20263,12 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -20283,22 +20283,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>124447866</v>
+        <v>124465031</v>
       </c>
       <c r="B169" t="n">
-        <v>79857</v>
+        <v>78810</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -20307,41 +20307,41 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>461220</v>
+        <v>460892</v>
       </c>
       <c r="R169" t="n">
-        <v>7050419</v>
+        <v>7050870</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>På död jolster vid bäck i fuktig gammal granskog</t>
+          <t>På gammal senvuxen gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20412,10 +20412,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>124463551</v>
+        <v>124459186</v>
       </c>
       <c r="B170" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -20428,21 +20428,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -20452,10 +20452,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>460829</v>
+        <v>460885</v>
       </c>
       <c r="R170" t="n">
-        <v>7051205</v>
+        <v>7051041</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -20487,7 +20487,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -20497,12 +20497,12 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>På levande gran I gammal barrblandskog</t>
+          <t>På gran ca 50 cm i diameter</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -20529,10 +20529,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>124457172</v>
+        <v>124465683</v>
       </c>
       <c r="B171" t="n">
-        <v>100279</v>
+        <v>79920</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -20545,34 +20545,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>222498</v>
+        <v>6462</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>460933</v>
+        <v>460934</v>
       </c>
       <c r="R171" t="n">
-        <v>7050887</v>
+        <v>7050676</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20604,7 +20604,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -20614,7 +20614,12 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>På gammal sälg i äldre granskog</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -20629,22 +20634,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>124454537</v>
+        <v>124459298</v>
       </c>
       <c r="B172" t="n">
-        <v>96985</v>
+        <v>79927</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -20657,34 +20662,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>221941</v>
+        <v>6464</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>460968</v>
+        <v>460882</v>
       </c>
       <c r="R172" t="n">
-        <v>7050710</v>
+        <v>7051046</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20716,7 +20721,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -20726,12 +20731,12 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På sälg ca 40 cm i diameter</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -20746,19 +20751,19 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>124465031</v>
+        <v>124466958</v>
       </c>
       <c r="B173" t="n">
         <v>78810</v>
@@ -20791,20 +20796,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr"/>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>460892</v>
+        <v>461083</v>
       </c>
       <c r="R173" t="n">
-        <v>7050870</v>
+        <v>7050465</v>
       </c>
       <c r="S173" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -20833,7 +20847,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -20843,12 +20857,12 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>På gammal senvuxen gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -20875,7 +20889,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>124459186</v>
+        <v>124464945</v>
       </c>
       <c r="B174" t="n">
         <v>74901</v>
@@ -20915,10 +20929,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>460885</v>
+        <v>460854</v>
       </c>
       <c r="R174" t="n">
-        <v>7051041</v>
+        <v>7050992</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20950,7 +20964,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -20960,12 +20974,12 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>På gran ca 50 cm i diameter</t>
+          <t>På gran ca 35 cm i diameter ca 7 m från bäck i gammal granskog</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20992,10 +21006,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>124465683</v>
+        <v>124447866</v>
       </c>
       <c r="B175" t="n">
-        <v>79920</v>
+        <v>79857</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -21008,34 +21022,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6462</v>
+        <v>229748</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>460934</v>
+        <v>461220</v>
       </c>
       <c r="R175" t="n">
-        <v>7050676</v>
+        <v>7050419</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -21067,7 +21081,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -21077,12 +21091,12 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>På gammal sälg i äldre granskog</t>
+          <t>På död jolster vid bäck i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -21109,10 +21123,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>124459298</v>
+        <v>124451578</v>
       </c>
       <c r="B176" t="n">
-        <v>79927</v>
+        <v>91012</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -21121,41 +21135,41 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>460882</v>
+        <v>461108</v>
       </c>
       <c r="R176" t="n">
-        <v>7051046</v>
+        <v>7050663</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -21184,7 +21198,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -21194,12 +21208,12 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>På sälg ca 40 cm i diameter</t>
+          <t>På granlåga i gammal granskog vid källflöde</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -21214,22 +21228,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>124466958</v>
+        <v>124457172</v>
       </c>
       <c r="B177" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -21238,47 +21252,38 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>461083</v>
+        <v>460933</v>
       </c>
       <c r="R177" t="n">
-        <v>7050465</v>
+        <v>7050887</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -21310,7 +21315,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -21320,12 +21325,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -21340,22 +21340,22 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>124464945</v>
+        <v>124454537</v>
       </c>
       <c r="B178" t="n">
-        <v>74901</v>
+        <v>96985</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -21364,38 +21364,38 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6440</v>
+        <v>221941</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>460854</v>
+        <v>460968</v>
       </c>
       <c r="R178" t="n">
-        <v>7050992</v>
+        <v>7050710</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -21427,7 +21427,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -21437,12 +21437,12 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter ca 7 m från bäck i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -21457,22 +21457,22 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124451578</v>
+        <v>124463551</v>
       </c>
       <c r="B179" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -21485,37 +21485,37 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>461108</v>
+        <v>460829</v>
       </c>
       <c r="R179" t="n">
-        <v>7050663</v>
+        <v>7051205</v>
       </c>
       <c r="S179" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -21554,12 +21554,12 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog vid källflöde</t>
+          <t>På levande gran I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -21574,12 +21574,12 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
@@ -22091,7 +22091,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124455697</v>
+        <v>124449557</v>
       </c>
       <c r="B184" t="n">
         <v>57513</v>
@@ -22127,7 +22127,7 @@
       <c r="I184" t="inlineStr"/>
       <c r="M184" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -22136,13 +22136,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>460906</v>
+        <v>461112</v>
       </c>
       <c r="R184" t="n">
-        <v>7050839</v>
+        <v>7050544</v>
       </c>
       <c r="S184" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -22181,12 +22181,12 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Lite äldre ringhack på gammal gran i gammal granskog på ås</t>
+          <t>Färska ringhack på gammal tall i gammal (150+) barrblandskog</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -22213,7 +22213,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124449557</v>
+        <v>124455697</v>
       </c>
       <c r="B185" t="n">
         <v>57513</v>
@@ -22249,7 +22249,7 @@
       <c r="I185" t="inlineStr"/>
       <c r="M185" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -22258,13 +22258,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>461112</v>
+        <v>460906</v>
       </c>
       <c r="R185" t="n">
-        <v>7050544</v>
+        <v>7050839</v>
       </c>
       <c r="S185" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -22303,12 +22303,12 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Färska ringhack på gammal tall i gammal (150+) barrblandskog</t>
+          <t>Lite äldre ringhack på gammal gran i gammal granskog på ås</t>
         </is>
       </c>
       <c r="AD185" t="b">

--- a/artfynd/A 12489-2025 artfynd.xlsx
+++ b/artfynd/A 12489-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124451344</v>
+        <v>124462929</v>
       </c>
       <c r="B2" t="n">
-        <v>77753</v>
+        <v>79428</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>314</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461120</v>
+        <v>460814</v>
       </c>
       <c r="R2" t="n">
-        <v>7050636</v>
+        <v>7051237</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På undersidan av gren på senvuxen gran ca 16 cm i diameter, intill bäck</t>
+          <t>På bränd högstubbe av tall i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124453534</v>
+        <v>124453753</v>
       </c>
       <c r="B3" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461003</v>
+        <v>460993</v>
       </c>
       <c r="R3" t="n">
-        <v>7050729</v>
+        <v>7050667</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På kvist på levande liten gran ca 3 cm i diameter I granskog på frisk-fuktig mark</t>
+          <t>På gamla granar vid bäck i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124462929</v>
+        <v>124457291</v>
       </c>
       <c r="B4" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460814</v>
+        <v>460917</v>
       </c>
       <c r="R4" t="n">
-        <v>7051237</v>
+        <v>7050904</v>
       </c>
       <c r="S4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På bränd högstubbe av tall i gammal barrblandskog</t>
+          <t>Ett tiotal bålar på en gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124453753</v>
+        <v>124466463</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,34 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460993</v>
+        <v>460999</v>
       </c>
       <c r="R5" t="n">
-        <v>7050667</v>
+        <v>7050500</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gamla granar vid bäck i gammal granskog</t>
+          <t>På gran ca 30 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1131,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124457291</v>
+        <v>124459487</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460917</v>
+        <v>460884</v>
       </c>
       <c r="R6" t="n">
-        <v>7050904</v>
+        <v>7051067</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ett tiotal bålar på en gran</t>
+          <t>På gran ca 40 cm i diameter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466463</v>
+        <v>124465595</v>
       </c>
       <c r="B7" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460999</v>
+        <v>460928</v>
       </c>
       <c r="R7" t="n">
-        <v>7050500</v>
+        <v>7050686</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran ca 30 cm i diameter i äldre barrblandskog</t>
+          <t>På gran ca 35 cm i diameter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,7 +1377,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124459487</v>
+        <v>124464548</v>
       </c>
       <c r="B8" t="n">
         <v>77743</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460884</v>
+        <v>460857</v>
       </c>
       <c r="R8" t="n">
-        <v>7051067</v>
+        <v>7051101</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran ca 40 cm i diameter</t>
+          <t>På senvuxen gran ca 15 cm i diameter I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124465595</v>
+        <v>124451344</v>
       </c>
       <c r="B9" t="n">
-        <v>77743</v>
+        <v>77753</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,34 +1510,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460928</v>
+        <v>461120</v>
       </c>
       <c r="R9" t="n">
-        <v>7050686</v>
+        <v>7050636</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter</t>
+          <t>På undersidan av gren på senvuxen gran ca 16 cm i diameter, intill bäck</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124464548</v>
+        <v>124453534</v>
       </c>
       <c r="B10" t="n">
-        <v>77743</v>
+        <v>78891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,21 +1627,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460857</v>
+        <v>461003</v>
       </c>
       <c r="R10" t="n">
-        <v>7051101</v>
+        <v>7050729</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På senvuxen gran ca 15 cm i diameter I gammal barrblandskog</t>
+          <t>På kvist på levande liten gran ca 3 cm i diameter I granskog på frisk-fuktig mark</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2781,10 +2781,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124464044</v>
+        <v>124447872</v>
       </c>
       <c r="B20" t="n">
-        <v>78455</v>
+        <v>77743</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2797,34 +2797,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460886</v>
+        <v>461229</v>
       </c>
       <c r="R20" t="n">
-        <v>7051158</v>
+        <v>7050409</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På ved på gammal tallrot på tallåga i gammal barrblandskog i sydsluttning</t>
+          <t>På gran ca 40 cm i diameter i äldre granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2886,22 +2886,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124463372</v>
+        <v>124464044</v>
       </c>
       <c r="B21" t="n">
-        <v>79851</v>
+        <v>78455</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2910,38 +2910,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460809</v>
+        <v>460886</v>
       </c>
       <c r="R21" t="n">
-        <v>7051220</v>
+        <v>7051158</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2983,12 +2983,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På döende sälg ca 45 cm i diameter I gammal barrblandskog</t>
+          <t>På ved på gammal tallrot på tallåga i gammal barrblandskog i sydsluttning</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3003,22 +3003,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124452305</v>
+        <v>124450863</v>
       </c>
       <c r="B22" t="n">
-        <v>79926</v>
+        <v>56714</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3027,38 +3027,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461106</v>
+        <v>461150</v>
       </c>
       <c r="R22" t="n">
-        <v>7050697</v>
+        <v>7050646</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3090,7 +3099,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3100,12 +3109,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal grov sälg i gammal granskog</t>
+          <t>I gammal granskog vid källflöde</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3132,10 +3141,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124467045</v>
+        <v>124463372</v>
       </c>
       <c r="B23" t="n">
-        <v>79920</v>
+        <v>79851</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3148,21 +3157,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3172,10 +3181,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461086</v>
+        <v>460809</v>
       </c>
       <c r="R23" t="n">
-        <v>7050465</v>
+        <v>7051220</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3207,7 +3216,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3217,12 +3226,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På rönn I äldre granskog</t>
+          <t>På döende sälg ca 45 cm i diameter I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3249,10 +3258,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124454161</v>
+        <v>124452305</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3261,20 +3270,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3285,14 +3294,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461010</v>
+        <v>461106</v>
       </c>
       <c r="R24" t="n">
-        <v>7050791</v>
+        <v>7050697</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3324,7 +3333,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3334,12 +3343,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ett tiotal bålar på en gran</t>
+          <t>På bark på stam av levande gammal grov sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3354,22 +3363,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124462439</v>
+        <v>124467045</v>
       </c>
       <c r="B25" t="n">
-        <v>79428</v>
+        <v>79920</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3378,25 +3387,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3406,10 +3415,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460848</v>
+        <v>461086</v>
       </c>
       <c r="R25" t="n">
-        <v>7051206</v>
+        <v>7050465</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3441,7 +3450,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3451,12 +3460,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På dimensionsavverkningsstubbe av tall i gammal gles barrblandskog</t>
+          <t>På rönn I äldre granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3483,7 +3492,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124458954</v>
+        <v>124454161</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3523,10 +3532,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460891</v>
+        <v>461010</v>
       </c>
       <c r="R26" t="n">
-        <v>7051023</v>
+        <v>7050791</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3558,7 +3567,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3568,12 +3577,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ett 30-tal bålar på 3 granar</t>
+          <t>Ett tiotal bålar på en gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3600,10 +3609,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124462400</v>
+        <v>124462439</v>
       </c>
       <c r="B27" t="n">
-        <v>74901</v>
+        <v>79428</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3616,21 +3625,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3640,10 +3649,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460862</v>
+        <v>460848</v>
       </c>
       <c r="R27" t="n">
-        <v>7051207</v>
+        <v>7051206</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3675,7 +3684,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3685,12 +3694,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter i gammal gles barrblandskog på blockrik mark</t>
+          <t>På dimensionsavverkningsstubbe av tall i gammal gles barrblandskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3717,10 +3726,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124447872</v>
+        <v>124458954</v>
       </c>
       <c r="B28" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3733,34 +3742,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461229</v>
+        <v>460891</v>
       </c>
       <c r="R28" t="n">
-        <v>7050409</v>
+        <v>7051023</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3792,7 +3801,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3802,12 +3811,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gran ca 40 cm i diameter i äldre granskog</t>
+          <t>Ett 30-tal bålar på 3 granar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3834,10 +3843,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124450863</v>
+        <v>124462400</v>
       </c>
       <c r="B29" t="n">
-        <v>56714</v>
+        <v>74901</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3850,43 +3859,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461150</v>
+        <v>460862</v>
       </c>
       <c r="R29" t="n">
-        <v>7050646</v>
+        <v>7051207</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>I gammal granskog vid källflöde</t>
+          <t>På gran ca 25 cm i diameter i gammal gles barrblandskog på blockrik mark</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3948,12 +3948,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4194,10 +4194,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124464465</v>
+        <v>124461212</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4210,34 +4210,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460851</v>
+        <v>460856</v>
       </c>
       <c r="R32" t="n">
-        <v>7051086</v>
+        <v>7051188</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På ved på gammal dimensionsavverkningsstubbe ca 35 cm i diameter och 1,3 meter hög. I öppen gles skog med gran, tall och björk på blockrik mark</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4299,22 +4299,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124461212</v>
+        <v>124452744</v>
       </c>
       <c r="B33" t="n">
-        <v>79428</v>
+        <v>91030</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4327,37 +4327,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460856</v>
+        <v>461081</v>
       </c>
       <c r="R33" t="n">
-        <v>7051188</v>
+        <v>7050715</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På ved på gammal dimensionsavverkningsstubbe ca 35 cm i diameter och 1,3 meter hög. I öppen gles skog med gran, tall och björk på blockrik mark</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4416,22 +4416,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124455518</v>
+        <v>124465552</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>79892</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4444,34 +4444,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460913</v>
+        <v>460923</v>
       </c>
       <c r="R34" t="n">
-        <v>7050818</v>
+        <v>7050686</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog på ås</t>
+          <t>På bark på stam av levande sälg i äldre granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4662,10 +4662,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124452744</v>
+        <v>124464465</v>
       </c>
       <c r="B36" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4678,37 +4678,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461081</v>
+        <v>460851</v>
       </c>
       <c r="R36" t="n">
-        <v>7050715</v>
+        <v>7051086</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4772,17 +4772,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124465552</v>
+        <v>124455518</v>
       </c>
       <c r="B37" t="n">
-        <v>79892</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4795,34 +4795,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460923</v>
+        <v>460913</v>
       </c>
       <c r="R37" t="n">
-        <v>7050686</v>
+        <v>7050818</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4864,12 +4864,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg i äldre granskog</t>
+          <t>På gammal granlåga i gammal granskog på ås</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5013,10 +5013,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124454594</v>
+        <v>124456509</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5025,38 +5025,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460975</v>
+        <v>460910</v>
       </c>
       <c r="R39" t="n">
-        <v>7050715</v>
+        <v>7050839</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5088,7 +5097,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5098,12 +5107,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog vid surdråg</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5130,10 +5139,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124452019</v>
+        <v>124454594</v>
       </c>
       <c r="B40" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5142,25 +5151,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5170,10 +5179,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461089</v>
+        <v>460975</v>
       </c>
       <c r="R40" t="n">
-        <v>7050682</v>
+        <v>7050715</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5205,7 +5214,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5215,12 +5224,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På gammal gran i gammal granskog vid surdråg</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5247,10 +5256,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124458985</v>
+        <v>124452019</v>
       </c>
       <c r="B41" t="n">
-        <v>79891</v>
+        <v>79927</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5259,25 +5268,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5287,10 +5296,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460902</v>
+        <v>461089</v>
       </c>
       <c r="R41" t="n">
-        <v>7051049</v>
+        <v>7050682</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5322,7 +5331,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5332,12 +5341,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På sälglåga i kanten av gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5364,10 +5373,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124455107</v>
+        <v>124458985</v>
       </c>
       <c r="B42" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5376,38 +5385,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>460938</v>
+        <v>460902</v>
       </c>
       <c r="R42" t="n">
-        <v>7050831</v>
+        <v>7051049</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5439,7 +5448,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5449,12 +5458,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På död rönn ca 18 cm i diameter</t>
+          <t>På sälglåga i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5469,22 +5478,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124466116</v>
+        <v>124455107</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5493,38 +5502,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>460933</v>
+        <v>460938</v>
       </c>
       <c r="R43" t="n">
-        <v>7050567</v>
+        <v>7050831</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5556,7 +5565,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5566,12 +5575,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På död rönn ca 18 cm i diameter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5586,22 +5595,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124454121</v>
+        <v>124466116</v>
       </c>
       <c r="B44" t="n">
-        <v>91950</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5610,38 +5619,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461008</v>
+        <v>460933</v>
       </c>
       <c r="R44" t="n">
-        <v>7050615</v>
+        <v>7050567</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5673,7 +5682,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5683,12 +5692,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På marken i bäckdråg  med gammal granskog med rikligt med död ved</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5715,7 +5724,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124452814</v>
+        <v>124454121</v>
       </c>
       <c r="B45" t="n">
         <v>91950</v>
@@ -5755,10 +5764,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461051</v>
+        <v>461008</v>
       </c>
       <c r="R45" t="n">
-        <v>7050735</v>
+        <v>7050615</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5790,7 +5799,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5800,12 +5809,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i bäckdråg  med gammal granskog med rikligt med död ved</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5832,10 +5841,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124453757</v>
+        <v>124452814</v>
       </c>
       <c r="B46" t="n">
-        <v>77743</v>
+        <v>91950</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5844,38 +5853,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228579</v>
+        <v>4769</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>460989</v>
+        <v>461051</v>
       </c>
       <c r="R46" t="n">
-        <v>7050753</v>
+        <v>7050735</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5907,7 +5916,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5917,12 +5926,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gran ca 45 cm i diameter</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5937,22 +5946,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124462884</v>
+        <v>124453757</v>
       </c>
       <c r="B47" t="n">
-        <v>78547</v>
+        <v>77743</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5965,21 +5974,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>228579</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5989,10 +5998,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>460813</v>
+        <v>460989</v>
       </c>
       <c r="R47" t="n">
-        <v>7051241</v>
+        <v>7050753</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6024,7 +6033,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6034,12 +6043,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På kol på bränd högstubbe av tall ca 35 cm i diameter och 2,5 m hög i äldre barrblandskog</t>
+          <t>På gran ca 45 cm i diameter</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6066,10 +6075,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124457471</v>
+        <v>124462884</v>
       </c>
       <c r="B48" t="n">
-        <v>77743</v>
+        <v>78547</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6082,21 +6091,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228579</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6106,10 +6115,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>460904</v>
+        <v>460813</v>
       </c>
       <c r="R48" t="n">
-        <v>7050918</v>
+        <v>7051241</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6141,7 +6150,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6151,12 +6160,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre granskog</t>
+          <t>På kol på bränd högstubbe av tall ca 35 cm i diameter och 2,5 m hög i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6183,10 +6192,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124456509</v>
+        <v>124457471</v>
       </c>
       <c r="B49" t="n">
-        <v>57883</v>
+        <v>77743</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6195,47 +6204,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103015</v>
+        <v>228579</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>460910</v>
+        <v>460904</v>
       </c>
       <c r="R49" t="n">
-        <v>7050839</v>
+        <v>7050918</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På gran ca 35 cm i diameter i äldre granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6297,12 +6297,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -10890,10 +10890,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124447843</v>
+        <v>124452335</v>
       </c>
       <c r="B89" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10902,25 +10902,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10930,10 +10930,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461226</v>
+        <v>461106</v>
       </c>
       <c r="R89" t="n">
-        <v>7050425</v>
+        <v>7050697</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10965,7 +10965,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10975,12 +10975,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På gran ca 40 cm i diameter i äldre granskog</t>
+          <t>På bark på stam av levande gammal grov sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10995,22 +10995,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124452335</v>
+        <v>124447843</v>
       </c>
       <c r="B90" t="n">
-        <v>79920</v>
+        <v>74901</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11019,25 +11019,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -11047,10 +11047,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461106</v>
+        <v>461226</v>
       </c>
       <c r="R90" t="n">
-        <v>7050697</v>
+        <v>7050425</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal grov sälg i gammal granskog</t>
+          <t>På gran ca 40 cm i diameter i äldre granskog</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11112,12 +11112,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -12415,10 +12415,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124458497</v>
+        <v>124465301</v>
       </c>
       <c r="B102" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12431,34 +12431,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>460925</v>
+        <v>460931</v>
       </c>
       <c r="R102" t="n">
-        <v>7051037</v>
+        <v>7050705</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12490,7 +12490,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12500,12 +12500,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>På gammal granlåga i kanten av gammal granskog</t>
+          <t>Ca 20 bålar på en gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12520,22 +12520,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124459560</v>
+        <v>124455021</v>
       </c>
       <c r="B103" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12548,21 +12548,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12572,10 +12572,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>460899</v>
+        <v>460949</v>
       </c>
       <c r="R103" t="n">
-        <v>7051069</v>
+        <v>7050826</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12607,7 +12607,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>På granlåga ca 35 cm i diameter, ligger över en bäck i en liten svacka/ravin</t>
+          <t>På gran ca 40 cm i diameter i äldre granskog på frisk-fuktig mark</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12649,10 +12649,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124449598</v>
+        <v>124457780</v>
       </c>
       <c r="B104" t="n">
-        <v>91030</v>
+        <v>74885</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12661,25 +12661,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12689,10 +12689,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461116</v>
+        <v>460884</v>
       </c>
       <c r="R104" t="n">
-        <v>7050579</v>
+        <v>7050944</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12724,7 +12724,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12734,12 +12734,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>På död del av levande gran ca 5 m från en bäck i äldre granskog</t>
+          <t>På ved på gråalshögstubbe i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12754,22 +12754,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124465301</v>
+        <v>124454557</v>
       </c>
       <c r="B105" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12778,38 +12778,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>460931</v>
+        <v>460965</v>
       </c>
       <c r="R105" t="n">
-        <v>7050705</v>
+        <v>7050714</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12841,7 +12841,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12851,12 +12851,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Ca 20 bålar på en gran i äldre granskog</t>
+          <t>På marken i gammal granskog vid gammal stig</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12871,22 +12871,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124455021</v>
+        <v>124465334</v>
       </c>
       <c r="B106" t="n">
-        <v>74901</v>
+        <v>79891</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12899,37 +12899,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>460949</v>
+        <v>460923</v>
       </c>
       <c r="R106" t="n">
-        <v>7050826</v>
+        <v>7050686</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12968,12 +12968,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>På gran ca 40 cm i diameter i äldre granskog på frisk-fuktig mark</t>
+          <t>På sälg i äldre granskog</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12988,22 +12988,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124457780</v>
+        <v>124458497</v>
       </c>
       <c r="B107" t="n">
-        <v>74885</v>
+        <v>91012</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13012,25 +13012,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -13040,10 +13040,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>460884</v>
+        <v>460925</v>
       </c>
       <c r="R107" t="n">
-        <v>7050944</v>
+        <v>7051037</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13075,7 +13075,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13085,12 +13085,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>På ved på gråalshögstubbe i gammal granskog på fuktig mark</t>
+          <t>På gammal granlåga i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13117,10 +13117,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124454557</v>
+        <v>124459560</v>
       </c>
       <c r="B108" t="n">
-        <v>79919</v>
+        <v>91012</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13129,38 +13129,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>460965</v>
+        <v>460899</v>
       </c>
       <c r="R108" t="n">
-        <v>7050714</v>
+        <v>7051069</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13192,7 +13192,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13202,12 +13202,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog vid gammal stig</t>
+          <t>På granlåga ca 35 cm i diameter, ligger över en bäck i en liten svacka/ravin</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13222,22 +13222,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124465334</v>
+        <v>124449598</v>
       </c>
       <c r="B109" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13250,37 +13250,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>460923</v>
+        <v>461116</v>
       </c>
       <c r="R109" t="n">
-        <v>7050686</v>
+        <v>7050579</v>
       </c>
       <c r="S109" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>På sälg i äldre granskog</t>
+          <t>På död del av levande gran ca 5 m från en bäck i äldre granskog</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13339,12 +13339,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -13468,10 +13468,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124449149</v>
+        <v>124453984</v>
       </c>
       <c r="B111" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13484,46 +13484,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>461138</v>
+        <v>460981</v>
       </c>
       <c r="R111" t="n">
-        <v>7050552</v>
+        <v>7050778</v>
       </c>
       <c r="S111" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13552,7 +13543,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13562,12 +13553,12 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gran ca 30 cm i diameter i äldre granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13582,22 +13573,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124453984</v>
+        <v>124456913</v>
       </c>
       <c r="B112" t="n">
-        <v>74901</v>
+        <v>79066</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13606,25 +13597,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6440</v>
+        <v>6459</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13634,10 +13625,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>460981</v>
+        <v>460944</v>
       </c>
       <c r="R112" t="n">
-        <v>7050778</v>
+        <v>7050864</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13669,7 +13660,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13679,12 +13670,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>På gran ca 30 cm i diameter i äldre granskog på fuktig mark</t>
+          <t>På sälg ca 15 cm i diameter</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13711,10 +13702,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124456913</v>
+        <v>124452903</v>
       </c>
       <c r="B113" t="n">
-        <v>79066</v>
+        <v>74901</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13723,25 +13714,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6459</v>
+        <v>6440</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13751,10 +13742,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>460944</v>
+        <v>461060</v>
       </c>
       <c r="R113" t="n">
-        <v>7050864</v>
+        <v>7050712</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13786,7 +13777,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13796,12 +13787,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>På sälg ca 15 cm i diameter</t>
+          <t>På gran ca 30 cm i diameter I äldre granskog</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13828,7 +13819,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124452903</v>
+        <v>124453195</v>
       </c>
       <c r="B114" t="n">
         <v>74901</v>
@@ -13864,17 +13855,17 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>461060</v>
+        <v>461036</v>
       </c>
       <c r="R114" t="n">
-        <v>7050712</v>
+        <v>7050719</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13903,7 +13894,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13913,12 +13904,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>På gran ca 30 cm i diameter I äldre granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13933,22 +13924,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124453195</v>
+        <v>124453283</v>
       </c>
       <c r="B115" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13961,21 +13952,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13985,13 +13976,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>461036</v>
+        <v>461018</v>
       </c>
       <c r="R115" t="n">
-        <v>7050719</v>
+        <v>7050712</v>
       </c>
       <c r="S115" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14020,7 +14011,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -14030,12 +14021,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14055,17 +14046,17 @@
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124453283</v>
+        <v>124449149</v>
       </c>
       <c r="B116" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14078,37 +14069,46 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>461018</v>
+        <v>461138</v>
       </c>
       <c r="R116" t="n">
-        <v>7050712</v>
+        <v>7050552</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14147,12 +14147,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14179,10 +14179,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124462686</v>
+        <v>124447955</v>
       </c>
       <c r="B117" t="n">
-        <v>79428</v>
+        <v>95335</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14191,38 +14191,38 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>2809</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>460844</v>
+        <v>461213</v>
       </c>
       <c r="R117" t="n">
-        <v>7051231</v>
+        <v>7050425</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14254,7 +14254,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14264,12 +14264,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>På dimensionsavverkningsstubbe av tall</t>
+          <t>På fuktig mark vid bäck i gammal granskog</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14284,22 +14284,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124454800</v>
+        <v>124454221</v>
       </c>
       <c r="B118" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14312,34 +14312,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>460959</v>
+        <v>460997</v>
       </c>
       <c r="R118" t="n">
-        <v>7050805</v>
+        <v>7050602</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14371,7 +14371,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -14381,12 +14381,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ett 100-tal bålar på ett 10-tal granar</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14401,22 +14401,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124457379</v>
+        <v>124452176</v>
       </c>
       <c r="B119" t="n">
-        <v>91950</v>
+        <v>77743</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14425,38 +14425,38 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4769</v>
+        <v>228579</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>460878</v>
+        <v>461093</v>
       </c>
       <c r="R119" t="n">
-        <v>7050927</v>
+        <v>7050684</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14488,7 +14488,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14498,12 +14498,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>På marken i gammal fuktig granskog</t>
+          <t>På gran ca 35 cm i diameter i äldre granskog med inslag av björk och tall</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14518,22 +14518,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124459530</v>
+        <v>124454733</v>
       </c>
       <c r="B120" t="n">
-        <v>74906</v>
+        <v>77743</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14546,34 +14546,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1467</v>
+        <v>228579</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>460879</v>
+        <v>460963</v>
       </c>
       <c r="R120" t="n">
-        <v>7051087</v>
+        <v>7050824</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14615,12 +14615,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>I hålighet vid basen av grov gammal gran i gammal granskog vid bäck</t>
+          <t>På gran ca 35 cm i diameter i granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14635,22 +14635,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124464713</v>
+        <v>124450168</v>
       </c>
       <c r="B121" t="n">
-        <v>91299</v>
+        <v>57666</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14663,37 +14663,51 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>460834</v>
+        <v>461133</v>
       </c>
       <c r="R121" t="n">
-        <v>7051057</v>
+        <v>7050555</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14722,7 +14736,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14732,12 +14746,12 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>I gammal granskog omgiven av sumpskog och myr</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14764,10 +14778,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124450168</v>
+        <v>124456983</v>
       </c>
       <c r="B122" t="n">
-        <v>57666</v>
+        <v>100279</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14776,55 +14790,41 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>461133</v>
+        <v>460930</v>
       </c>
       <c r="R122" t="n">
-        <v>7050555</v>
+        <v>7050862</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>I gammal granskog omgiven av sumpskog och myr</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14895,7 +14895,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124456983</v>
+        <v>124453365</v>
       </c>
       <c r="B123" t="n">
         <v>100279</v>
@@ -14931,14 +14931,14 @@
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>460930</v>
+        <v>461017</v>
       </c>
       <c r="R123" t="n">
-        <v>7050862</v>
+        <v>7050715</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14980,12 +14980,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15000,22 +14995,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124453365</v>
+        <v>124448067</v>
       </c>
       <c r="B124" t="n">
-        <v>100279</v>
+        <v>74901</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15024,38 +15019,38 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>222498</v>
+        <v>6440</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>461017</v>
+        <v>461238</v>
       </c>
       <c r="R124" t="n">
-        <v>7050715</v>
+        <v>7050458</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15087,7 +15082,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15097,7 +15092,12 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>På gran ca 45 cm i diameter i äldre granskog med inslag av tall</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15124,10 +15124,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124454221</v>
+        <v>124462686</v>
       </c>
       <c r="B125" t="n">
-        <v>77743</v>
+        <v>79428</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -15140,34 +15140,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228579</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>460997</v>
+        <v>460844</v>
       </c>
       <c r="R125" t="n">
-        <v>7050602</v>
+        <v>7051231</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15209,12 +15209,12 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15229,22 +15229,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>124452176</v>
+        <v>124454800</v>
       </c>
       <c r="B126" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -15257,21 +15257,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -15281,10 +15281,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>461093</v>
+        <v>460959</v>
       </c>
       <c r="R126" t="n">
-        <v>7050684</v>
+        <v>7050805</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -15326,12 +15326,12 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre granskog med inslag av björk och tall</t>
+          <t>Ett 100-tal bålar på ett 10-tal granar</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15358,10 +15358,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>124454733</v>
+        <v>124457379</v>
       </c>
       <c r="B127" t="n">
-        <v>77743</v>
+        <v>91950</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15370,38 +15370,38 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228579</v>
+        <v>4769</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>460963</v>
+        <v>460878</v>
       </c>
       <c r="R127" t="n">
-        <v>7050824</v>
+        <v>7050927</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15433,7 +15433,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15443,12 +15443,12 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i granskog på fuktig mark</t>
+          <t>På marken i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15463,22 +15463,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>124448067</v>
+        <v>124459530</v>
       </c>
       <c r="B128" t="n">
-        <v>74901</v>
+        <v>74906</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15491,34 +15491,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>461238</v>
+        <v>460879</v>
       </c>
       <c r="R128" t="n">
-        <v>7050458</v>
+        <v>7051087</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15550,7 +15550,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15560,12 +15560,12 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>På gran ca 45 cm i diameter i äldre granskog med inslag av tall</t>
+          <t>I hålighet vid basen av grov gammal gran i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15580,22 +15580,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124447955</v>
+        <v>124464713</v>
       </c>
       <c r="B129" t="n">
-        <v>95335</v>
+        <v>91299</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15604,38 +15604,38 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>461213</v>
+        <v>460834</v>
       </c>
       <c r="R129" t="n">
-        <v>7050425</v>
+        <v>7051057</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15667,7 +15667,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15677,12 +15677,12 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>På fuktig mark vid bäck i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15709,10 +15709,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124459169</v>
+        <v>124449498</v>
       </c>
       <c r="B130" t="n">
-        <v>91012</v>
+        <v>77743</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15725,34 +15725,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>460887</v>
+        <v>461115</v>
       </c>
       <c r="R130" t="n">
-        <v>7051060</v>
+        <v>7050559</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15794,12 +15794,12 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal gran ca 20 cm I diameter I äldre granskog med tallinslag</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15814,22 +15814,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>124455106</v>
+        <v>124458130</v>
       </c>
       <c r="B131" t="n">
-        <v>98101</v>
+        <v>79892</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15838,55 +15838,41 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>460928</v>
+        <v>460978</v>
       </c>
       <c r="R131" t="n">
-        <v>7050799</v>
+        <v>7050963</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15915,7 +15901,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15925,12 +15911,12 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>37 plantor inom 0,5x0,5 meter, många små och unga plantor men även en vinterståndare. Intill gammal igenväxande fäbodstig.</t>
+          <t>På bark vid basen av gammal levande sälg i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15950,17 +15936,17 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>124453869</v>
+        <v>124458517</v>
       </c>
       <c r="B132" t="n">
-        <v>80783</v>
+        <v>79892</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15973,34 +15959,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>229436</v>
+        <v>2081</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Halmgul örnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Ochrolechia alboflavescens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Wulfen) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>461025</v>
+        <v>460887</v>
       </c>
       <c r="R132" t="n">
-        <v>7050650</v>
+        <v>7051004</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -16032,7 +16018,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -16042,12 +16028,12 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>På bark på död gren på gammal levande gran i gammal granskog</t>
+          <t>På sälg ca 45 cm i diameter</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16062,22 +16048,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>124452541</v>
+        <v>124459169</v>
       </c>
       <c r="B133" t="n">
-        <v>77743</v>
+        <v>91012</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -16090,34 +16076,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>461068</v>
+        <v>460887</v>
       </c>
       <c r="R133" t="n">
-        <v>7050690</v>
+        <v>7051060</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16149,7 +16135,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -16159,12 +16145,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>På gran ca 45 cm i diameter i äldre granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16179,22 +16165,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>124449498</v>
+        <v>124455106</v>
       </c>
       <c r="B134" t="n">
-        <v>77743</v>
+        <v>98101</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16203,38 +16189,52 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>461115</v>
+        <v>460928</v>
       </c>
       <c r="R134" t="n">
-        <v>7050559</v>
+        <v>7050799</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16266,7 +16266,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -16276,12 +16276,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>På gammal gran ca 20 cm I diameter I äldre granskog med tallinslag</t>
+          <t>37 plantor inom 0,5x0,5 meter, många små och unga plantor men även en vinterståndare. Intill gammal igenväxande fäbodstig.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16296,22 +16296,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124458130</v>
+        <v>124453869</v>
       </c>
       <c r="B135" t="n">
-        <v>79892</v>
+        <v>80783</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16324,21 +16324,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2081</v>
+        <v>229436</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Halmgul örnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ochrolechia alboflavescens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Wulfen) Zahlbr.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -16348,13 +16348,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>460978</v>
+        <v>461025</v>
       </c>
       <c r="R135" t="n">
-        <v>7050963</v>
+        <v>7050650</v>
       </c>
       <c r="S135" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -16393,12 +16393,12 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande sälg i gammal granskog på fuktig mark</t>
+          <t>På bark på död gren på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16425,10 +16425,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>124458517</v>
+        <v>124452541</v>
       </c>
       <c r="B136" t="n">
-        <v>79892</v>
+        <v>77743</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16441,21 +16441,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -16465,10 +16465,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>460887</v>
+        <v>461068</v>
       </c>
       <c r="R136" t="n">
-        <v>7051004</v>
+        <v>7050690</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>På sälg ca 45 cm i diameter</t>
+          <t>På gran ca 45 cm i diameter i äldre granskog</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -18648,10 +18648,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124464212</v>
+        <v>124453554</v>
       </c>
       <c r="B155" t="n">
-        <v>78547</v>
+        <v>91012</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18664,37 +18664,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>460841</v>
+        <v>461012</v>
       </c>
       <c r="R155" t="n">
-        <v>7051180</v>
+        <v>7050679</v>
       </c>
       <c r="S155" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18733,12 +18733,12 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallhögstubbe i gammal granskog</t>
+          <t>På granlåga i fuktigt läge vid bäckdråg, i gammal granskog</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18765,10 +18765,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124447855</v>
+        <v>124459477</v>
       </c>
       <c r="B156" t="n">
-        <v>79920</v>
+        <v>57529</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18777,41 +18777,46 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>461216</v>
+        <v>460890</v>
       </c>
       <c r="R156" t="n">
-        <v>7050415</v>
+        <v>7051075</v>
       </c>
       <c r="S156" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18840,7 +18845,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18850,12 +18855,12 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>På bark på död stam av jolster i fuktig gammal granskog vid bäck</t>
+          <t>Födosökspår efter hästmyror</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18882,10 +18887,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>124453554</v>
+        <v>124464212</v>
       </c>
       <c r="B157" t="n">
-        <v>91012</v>
+        <v>78547</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18898,37 +18903,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>461012</v>
+        <v>460841</v>
       </c>
       <c r="R157" t="n">
-        <v>7050679</v>
+        <v>7051180</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -18957,7 +18962,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18967,12 +18972,12 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>På granlåga i fuktigt läge vid bäckdråg, i gammal granskog</t>
+          <t>På kolad ved på gammal tallhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18999,10 +19004,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>124459477</v>
+        <v>124447855</v>
       </c>
       <c r="B158" t="n">
-        <v>57529</v>
+        <v>79920</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -19011,46 +19016,41 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>460890</v>
+        <v>461216</v>
       </c>
       <c r="R158" t="n">
-        <v>7051075</v>
+        <v>7050415</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -19089,12 +19089,12 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Födosökspår efter hästmyror</t>
+          <t>På bark på död stam av jolster i fuktig gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -19121,10 +19121,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>124456604</v>
+        <v>124447135</v>
       </c>
       <c r="B159" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -19137,21 +19137,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -19161,10 +19161,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>460930</v>
+        <v>461248</v>
       </c>
       <c r="R159" t="n">
-        <v>7050842</v>
+        <v>7050401</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19196,7 +19196,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19206,12 +19206,12 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Rikligt på gammal sälg i gammal granskog</t>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19238,10 +19238,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>124451942</v>
+        <v>124459246</v>
       </c>
       <c r="B160" t="n">
-        <v>79891</v>
+        <v>91457</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -19250,41 +19250,41 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>461096</v>
+        <v>460886</v>
       </c>
       <c r="R160" t="n">
-        <v>7050682</v>
+        <v>7051067</v>
       </c>
       <c r="S160" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19323,12 +19323,12 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>Rikligt på granlåga i fuktigt läge ganska nära bäck, i gammal granskog</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19348,17 +19348,17 @@
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>124460160</v>
+        <v>124456604</v>
       </c>
       <c r="B161" t="n">
-        <v>79919</v>
+        <v>79891</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -19367,50 +19367,41 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>460878</v>
+        <v>460930</v>
       </c>
       <c r="R161" t="n">
-        <v>7051147</v>
+        <v>7050842</v>
       </c>
       <c r="S161" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -19439,7 +19430,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19449,12 +19440,12 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Rikligt på marken i fuktig sänka med rejält gammal granskog</t>
+          <t>Rikligt på gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19481,10 +19472,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>124458002</v>
+        <v>124451942</v>
       </c>
       <c r="B162" t="n">
-        <v>74901</v>
+        <v>79891</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -19497,37 +19488,37 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>460898</v>
+        <v>461096</v>
       </c>
       <c r="R162" t="n">
-        <v>7050962</v>
+        <v>7050682</v>
       </c>
       <c r="S162" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -19556,7 +19547,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -19566,12 +19557,12 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19586,22 +19577,22 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>124459044</v>
+        <v>124460160</v>
       </c>
       <c r="B163" t="n">
-        <v>74901</v>
+        <v>79919</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -19610,41 +19601,50 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>460900</v>
+        <v>460878</v>
       </c>
       <c r="R163" t="n">
-        <v>7051032</v>
+        <v>7051147</v>
       </c>
       <c r="S163" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -19683,12 +19683,12 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter</t>
+          <t>Rikligt på marken i fuktig sänka med rejält gammal granskog</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19703,22 +19703,22 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>124455549</v>
+        <v>124458002</v>
       </c>
       <c r="B164" t="n">
-        <v>79920</v>
+        <v>74901</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -19727,25 +19727,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -19755,10 +19755,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>460935</v>
+        <v>460898</v>
       </c>
       <c r="R164" t="n">
-        <v>7050779</v>
+        <v>7050962</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19790,7 +19790,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -19800,12 +19800,12 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>På sälg ca 45 cm i diameter</t>
+          <t>På gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19832,10 +19832,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>124448758</v>
+        <v>124459044</v>
       </c>
       <c r="B165" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -19848,34 +19848,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>461238</v>
+        <v>460900</v>
       </c>
       <c r="R165" t="n">
-        <v>7050458</v>
+        <v>7051032</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19907,7 +19907,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19917,12 +19917,12 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre granskog på frisk-fuktig mark</t>
+          <t>På gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19949,10 +19949,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>124449387</v>
+        <v>124455549</v>
       </c>
       <c r="B166" t="n">
-        <v>77743</v>
+        <v>79920</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19961,38 +19961,38 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>461132</v>
+        <v>460935</v>
       </c>
       <c r="R166" t="n">
-        <v>7050550</v>
+        <v>7050779</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -20024,7 +20024,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -20034,7 +20034,12 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>På sälg ca 45 cm i diameter</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -20061,10 +20066,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>124459246</v>
+        <v>124448758</v>
       </c>
       <c r="B167" t="n">
-        <v>91457</v>
+        <v>77743</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -20073,38 +20078,38 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1209</v>
+        <v>228579</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>460886</v>
+        <v>461238</v>
       </c>
       <c r="R167" t="n">
-        <v>7051067</v>
+        <v>7050458</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -20136,7 +20141,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -20146,12 +20151,12 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Rikligt på granlåga i fuktigt läge ganska nära bäck, i gammal granskog</t>
+          <t>På gran ca 35 cm i diameter i äldre granskog på frisk-fuktig mark</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20166,22 +20171,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>124447135</v>
+        <v>124449387</v>
       </c>
       <c r="B168" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -20194,21 +20199,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -20218,10 +20223,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>461248</v>
+        <v>461132</v>
       </c>
       <c r="R168" t="n">
-        <v>7050401</v>
+        <v>7050550</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -20253,7 +20258,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -20263,12 +20268,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>10:12</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -20283,12 +20283,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>

--- a/artfynd/A 12489-2025 artfynd.xlsx
+++ b/artfynd/A 12489-2025 artfynd.xlsx
@@ -21726,7 +21726,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124455697</v>
+        <v>124447394</v>
       </c>
       <c r="B181" t="n">
         <v>57513</v>
@@ -21771,13 +21771,13 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>460906</v>
+        <v>461261</v>
       </c>
       <c r="R181" t="n">
-        <v>7050839</v>
+        <v>7050414</v>
       </c>
       <c r="S181" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -21816,12 +21816,12 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Lite äldre ringhack på gammal gran i gammal granskog på ås</t>
+          <t>Ringhack, något år gamla, på gammal gran i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21848,7 +21848,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124449557</v>
+        <v>124455697</v>
       </c>
       <c r="B182" t="n">
         <v>57513</v>
@@ -21884,7 +21884,7 @@
       <c r="I182" t="inlineStr"/>
       <c r="M182" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -21893,13 +21893,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>461112</v>
+        <v>460906</v>
       </c>
       <c r="R182" t="n">
-        <v>7050544</v>
+        <v>7050839</v>
       </c>
       <c r="S182" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -21938,12 +21938,12 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Färska ringhack på gammal tall i gammal (150+) barrblandskog</t>
+          <t>Lite äldre ringhack på gammal gran i gammal granskog på ås</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21970,32 +21970,32 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124455432</v>
+        <v>124455015</v>
       </c>
       <c r="B183" t="n">
-        <v>57513</v>
+        <v>57454</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100109</v>
+        <v>102622</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -22003,10 +22003,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -22015,13 +22019,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>460912</v>
+        <v>460885</v>
       </c>
       <c r="R183" t="n">
-        <v>7050788</v>
+        <v>7050930</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -22050,7 +22054,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -22060,12 +22064,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>Relativt färska ringhack på gammal gran i gammal granskog vid ås och kärr</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -22092,7 +22091,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124448100</v>
+        <v>124449557</v>
       </c>
       <c r="B184" t="n">
         <v>57513</v>
@@ -22128,7 +22127,7 @@
       <c r="I184" t="inlineStr"/>
       <c r="M184" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -22137,13 +22136,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>461236</v>
+        <v>461112</v>
       </c>
       <c r="R184" t="n">
-        <v>7050434</v>
+        <v>7050544</v>
       </c>
       <c r="S184" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -22172,7 +22171,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -22182,12 +22181,12 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Rikliga, lite äldre ringhack 1-7 meter upp i gammal gran i gammal granskog</t>
+          <t>Färska ringhack på gammal tall i gammal (150+) barrblandskog</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -22214,7 +22213,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124447394</v>
+        <v>124455432</v>
       </c>
       <c r="B185" t="n">
         <v>57513</v>
@@ -22250,7 +22249,7 @@
       <c r="I185" t="inlineStr"/>
       <c r="M185" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -22259,10 +22258,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>461261</v>
+        <v>460912</v>
       </c>
       <c r="R185" t="n">
-        <v>7050414</v>
+        <v>7050788</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -22294,7 +22293,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -22304,12 +22303,12 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Ringhack, något år gamla, på gammal gran i kanten av gammal granskog</t>
+          <t>Relativt färska ringhack på gammal gran i gammal granskog vid ås och kärr</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -22336,32 +22335,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124455015</v>
+        <v>124448100</v>
       </c>
       <c r="B186" t="n">
-        <v>57454</v>
+        <v>57513</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>102622</v>
+        <v>100109</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -22369,14 +22368,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="M186" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
@@ -22385,13 +22380,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>460885</v>
+        <v>461236</v>
       </c>
       <c r="R186" t="n">
-        <v>7050930</v>
+        <v>7050434</v>
       </c>
       <c r="S186" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -22420,7 +22415,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -22430,7 +22425,12 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Rikliga, lite äldre ringhack 1-7 meter upp i gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -22450,7 +22450,7 @@
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>

--- a/artfynd/A 12489-2025 artfynd.xlsx
+++ b/artfynd/A 12489-2025 artfynd.xlsx
@@ -21726,10 +21726,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124447394</v>
+        <v>124455432</v>
       </c>
       <c r="B181" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
       <c r="I181" t="inlineStr"/>
       <c r="M181" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -21771,10 +21771,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>461261</v>
+        <v>460912</v>
       </c>
       <c r="R181" t="n">
-        <v>7050414</v>
+        <v>7050788</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -21806,7 +21806,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -21816,12 +21816,12 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Ringhack, något år gamla, på gammal gran i kanten av gammal granskog</t>
+          <t>Relativt färska ringhack på gammal gran i gammal granskog vid ås och kärr</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21848,32 +21848,32 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124455697</v>
+        <v>124455015</v>
       </c>
       <c r="B182" t="n">
-        <v>57513</v>
+        <v>57471</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100109</v>
+        <v>102622</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -21881,10 +21881,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -21893,13 +21897,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>460906</v>
+        <v>460885</v>
       </c>
       <c r="R182" t="n">
-        <v>7050839</v>
+        <v>7050930</v>
       </c>
       <c r="S182" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21928,7 +21932,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -21938,12 +21942,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>Lite äldre ringhack på gammal gran i gammal granskog på ås</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21970,32 +21969,32 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124455015</v>
+        <v>124447394</v>
       </c>
       <c r="B183" t="n">
-        <v>57454</v>
+        <v>57635</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>102622</v>
+        <v>100109</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -22003,14 +22002,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I183" t="inlineStr"/>
       <c r="M183" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -22019,13 +22014,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>460885</v>
+        <v>461261</v>
       </c>
       <c r="R183" t="n">
-        <v>7050930</v>
+        <v>7050414</v>
       </c>
       <c r="S183" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -22054,7 +22049,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -22064,7 +22059,12 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>Ringhack, något år gamla, på gammal gran i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -22094,7 +22094,7 @@
         <v>124449557</v>
       </c>
       <c r="B184" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -22213,10 +22213,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124455432</v>
+        <v>124456467</v>
       </c>
       <c r="B185" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -22249,7 +22249,7 @@
       <c r="I185" t="inlineStr"/>
       <c r="M185" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -22258,10 +22258,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>460912</v>
+        <v>460918</v>
       </c>
       <c r="R185" t="n">
-        <v>7050788</v>
+        <v>7050834</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -22293,7 +22293,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -22303,12 +22303,12 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack på gammal gran i gammal granskog vid ås och kärr</t>
+          <t>Rejält gamla ringhack på rejält gammal gran i gammal granskog på ås</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -22335,10 +22335,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124448100</v>
+        <v>124455697</v>
       </c>
       <c r="B186" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -22380,10 +22380,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>461236</v>
+        <v>460906</v>
       </c>
       <c r="R186" t="n">
-        <v>7050434</v>
+        <v>7050839</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -22415,7 +22415,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -22425,12 +22425,12 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Rikliga, lite äldre ringhack 1-7 meter upp i gammal gran i gammal granskog</t>
+          <t>Lite äldre ringhack på gammal gran i gammal granskog på ås</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -22450,17 +22450,17 @@
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124456467</v>
+        <v>124448100</v>
       </c>
       <c r="B187" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -22502,13 +22502,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>460918</v>
+        <v>461236</v>
       </c>
       <c r="R187" t="n">
-        <v>7050834</v>
+        <v>7050434</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -22547,12 +22547,12 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Rejält gamla ringhack på rejält gammal gran i gammal granskog på ås</t>
+          <t>Rikliga, lite äldre ringhack 1-7 meter upp i gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD187" t="b">

--- a/artfynd/A 12489-2025 artfynd.xlsx
+++ b/artfynd/A 12489-2025 artfynd.xlsx
@@ -21726,32 +21726,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124455432</v>
+        <v>124455015</v>
       </c>
       <c r="B181" t="n">
-        <v>57635</v>
+        <v>57471</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100109</v>
+        <v>102622</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -21759,10 +21759,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -21771,13 +21775,13 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>460912</v>
+        <v>460885</v>
       </c>
       <c r="R181" t="n">
-        <v>7050788</v>
+        <v>7050930</v>
       </c>
       <c r="S181" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -21806,7 +21810,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -21816,12 +21820,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>Relativt färska ringhack på gammal gran i gammal granskog vid ås och kärr</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21848,32 +21847,32 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124455015</v>
+        <v>124455432</v>
       </c>
       <c r="B182" t="n">
-        <v>57471</v>
+        <v>57635</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>102622</v>
+        <v>100109</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -21881,14 +21880,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I182" t="inlineStr"/>
       <c r="M182" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -21897,13 +21892,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>460885</v>
+        <v>460912</v>
       </c>
       <c r="R182" t="n">
-        <v>7050930</v>
+        <v>7050788</v>
       </c>
       <c r="S182" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21932,7 +21927,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -21942,7 +21937,12 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Relativt färska ringhack på gammal gran i gammal granskog vid ås och kärr</t>
         </is>
       </c>
       <c r="AD182" t="b">

--- a/artfynd/A 12489-2025 artfynd.xlsx
+++ b/artfynd/A 12489-2025 artfynd.xlsx
@@ -21726,32 +21726,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124455015</v>
+        <v>124456467</v>
       </c>
       <c r="B181" t="n">
-        <v>57471</v>
+        <v>57635</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>102622</v>
+        <v>100109</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -21759,14 +21759,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I181" t="inlineStr"/>
       <c r="M181" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -21775,13 +21771,13 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>460885</v>
+        <v>460918</v>
       </c>
       <c r="R181" t="n">
-        <v>7050930</v>
+        <v>7050834</v>
       </c>
       <c r="S181" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -21810,7 +21806,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -21820,7 +21816,12 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>Rejält gamla ringhack på rejält gammal gran i gammal granskog på ås</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21840,14 +21841,14 @@
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124455432</v>
+        <v>124449557</v>
       </c>
       <c r="B182" t="n">
         <v>57635</v>
@@ -21892,13 +21893,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>460912</v>
+        <v>461112</v>
       </c>
       <c r="R182" t="n">
-        <v>7050788</v>
+        <v>7050544</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21927,7 +21928,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -21937,12 +21938,12 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack på gammal gran i gammal granskog vid ås och kärr</t>
+          <t>Färska ringhack på gammal tall i gammal (150+) barrblandskog</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21969,7 +21970,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124447394</v>
+        <v>124448100</v>
       </c>
       <c r="B183" t="n">
         <v>57635</v>
@@ -22014,13 +22015,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>461261</v>
+        <v>461236</v>
       </c>
       <c r="R183" t="n">
-        <v>7050414</v>
+        <v>7050434</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -22049,7 +22050,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -22059,12 +22060,12 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Ringhack, något år gamla, på gammal gran i kanten av gammal granskog</t>
+          <t>Rikliga, lite äldre ringhack 1-7 meter upp i gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -22091,7 +22092,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124449557</v>
+        <v>124455432</v>
       </c>
       <c r="B184" t="n">
         <v>57635</v>
@@ -22136,13 +22137,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>461112</v>
+        <v>460912</v>
       </c>
       <c r="R184" t="n">
-        <v>7050544</v>
+        <v>7050788</v>
       </c>
       <c r="S184" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -22171,7 +22172,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -22181,12 +22182,12 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Färska ringhack på gammal tall i gammal (150+) barrblandskog</t>
+          <t>Relativt färska ringhack på gammal gran i gammal granskog vid ås och kärr</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -22213,7 +22214,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124456467</v>
+        <v>124455697</v>
       </c>
       <c r="B185" t="n">
         <v>57635</v>
@@ -22258,13 +22259,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>460918</v>
+        <v>460906</v>
       </c>
       <c r="R185" t="n">
-        <v>7050834</v>
+        <v>7050839</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -22293,7 +22294,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -22303,12 +22304,12 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Rejält gamla ringhack på rejält gammal gran i gammal granskog på ås</t>
+          <t>Lite äldre ringhack på gammal gran i gammal granskog på ås</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -22335,7 +22336,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124455697</v>
+        <v>124447394</v>
       </c>
       <c r="B186" t="n">
         <v>57635</v>
@@ -22380,13 +22381,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>460906</v>
+        <v>461261</v>
       </c>
       <c r="R186" t="n">
-        <v>7050839</v>
+        <v>7050414</v>
       </c>
       <c r="S186" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -22415,7 +22416,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -22425,12 +22426,12 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Lite äldre ringhack på gammal gran i gammal granskog på ås</t>
+          <t>Ringhack, något år gamla, på gammal gran i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -22450,39 +22451,39 @@
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124448100</v>
+        <v>124455015</v>
       </c>
       <c r="B187" t="n">
-        <v>57635</v>
+        <v>57471</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100109</v>
+        <v>102622</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -22490,10 +22491,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr"/>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
@@ -22502,13 +22507,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>461236</v>
+        <v>460885</v>
       </c>
       <c r="R187" t="n">
-        <v>7050434</v>
+        <v>7050930</v>
       </c>
       <c r="S187" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -22537,7 +22542,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -22547,12 +22552,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>Rikliga, lite äldre ringhack 1-7 meter upp i gammal gran i gammal granskog</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD187" t="b">
